--- a/Proyecto Interno/food-security-paper/input/cpi-weights/cpi-weights-2024.xlsx
+++ b/Proyecto Interno/food-security-paper/input/cpi-weights/cpi-weights-2024.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20374"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sergio.barona\Desktop\Least-cost-diets-and-affordability\Proyecto Interno\food-security-paper\input\cpi-weights\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f8f89820ab55adc2/Escritorio/Least-cost-diets-and-affordability/Proyecto Interno/food-security-paper/input/cpi-weights/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2D5BA2A4-4152-4BB4-8BE1-0033CFEC96F2}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="8_{2D5BA2A4-4152-4BB4-8BE1-0033CFEC96F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{376E6DF2-E185-4E8C-8317-5C5A6B1F60BB}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7545" xr2:uid="{FC0985A5-5039-410A-ABAD-69957A2833E5}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{FC0985A5-5039-410A-ABAD-69957A2833E5}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -5772,156 +5772,153 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="justify" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -5941,9 +5938,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - Tema de 2022">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -5981,7 +5978,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -6087,7 +6084,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -6229,7 +6226,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -6238,35 +6235,35 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B0FC014D-00B2-4C13-91A4-2AA847BBB61B}">
   <dimension ref="A1:L762"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.28515625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="11.7109375" style="3" customWidth="1"/>
-    <col min="3" max="3" width="10.28515625" style="4" customWidth="1"/>
-    <col min="4" max="4" width="31.7109375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="79.7109375" style="1" customWidth="1"/>
-    <col min="6" max="6" width="12.28515625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="11.42578125" style="1"/>
-    <col min="8" max="8" width="12.28515625" style="1" customWidth="1"/>
-    <col min="9" max="9" width="9.7109375" style="1" customWidth="1"/>
-    <col min="10" max="10" width="12.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="11.42578125" style="1"/>
+    <col min="1" max="1" width="13.33203125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="11.6640625" style="3" customWidth="1"/>
+    <col min="3" max="3" width="34.88671875" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="31.6640625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="108.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.33203125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="11.44140625" style="1"/>
+    <col min="8" max="8" width="12.33203125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="9.6640625" style="1" customWidth="1"/>
+    <col min="10" max="10" width="12.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="11.44140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="55" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="52" t="s">
+    <row r="1" spans="1:12" s="53" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="50" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="53" t="s">
+      <c r="B1" s="51" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="52" t="s">
+      <c r="C1" s="50" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="52" t="s">
+      <c r="D1" s="50" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="52" t="s">
+      <c r="E1" s="50" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="2" t="s">
@@ -6284,10 +6281,10 @@
       <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="54"/>
-      <c r="L1" s="54"/>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="K1" s="52"/>
+      <c r="L1" s="52"/>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>10</v>
       </c>
@@ -6313,7 +6310,7 @@
         <v>8.16</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>13</v>
       </c>
@@ -6339,7 +6336,7 @@
         <v>7.51</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>16</v>
       </c>
@@ -6365,7 +6362,7 @@
         <v>1.07</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>19</v>
       </c>
@@ -6391,7 +6388,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" s="7" t="s">
         <v>22</v>
       </c>
@@ -6415,7 +6412,7 @@
       <c r="K6" s="11"/>
       <c r="L6" s="11"/>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>19</v>
       </c>
@@ -6441,7 +6438,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="76.5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" ht="79.2" x14ac:dyDescent="0.3">
       <c r="A8" s="7" t="s">
         <v>22</v>
       </c>
@@ -6465,7 +6462,7 @@
       <c r="K8" s="11"/>
       <c r="L8" s="11"/>
     </row>
-    <row r="9" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A9" s="7" t="s">
         <v>22</v>
       </c>
@@ -6489,7 +6486,7 @@
       <c r="K9" s="16"/>
       <c r="L9" s="16"/>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" s="17" t="s">
         <v>19</v>
       </c>
@@ -6517,7 +6514,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11" s="7" t="s">
         <v>22</v>
       </c>
@@ -6541,7 +6538,7 @@
       <c r="K11" s="11"/>
       <c r="L11" s="11"/>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" s="17" t="s">
         <v>19</v>
       </c>
@@ -6569,7 +6566,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="13" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A13" s="7" t="s">
         <v>22</v>
       </c>
@@ -6593,7 +6590,7 @@
       <c r="K13" s="16"/>
       <c r="L13" s="16"/>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>19</v>
       </c>
@@ -6619,7 +6616,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="15" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A15" s="7" t="s">
         <v>22</v>
       </c>
@@ -6643,7 +6640,7 @@
       <c r="K15" s="16"/>
       <c r="L15" s="16"/>
     </row>
-    <row r="16" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A16" s="7" t="s">
         <v>22</v>
       </c>
@@ -6667,7 +6664,7 @@
       <c r="K16" s="16"/>
       <c r="L16" s="16"/>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>19</v>
       </c>
@@ -6693,7 +6690,7 @@
         <v>0.31</v>
       </c>
     </row>
-    <row r="18" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A18" s="7" t="s">
         <v>22</v>
       </c>
@@ -6717,7 +6714,7 @@
       <c r="K18" s="16"/>
       <c r="L18" s="16"/>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19" s="17" t="s">
         <v>19</v>
       </c>
@@ -6747,7 +6744,7 @@
       <c r="K19" s="17"/>
       <c r="L19" s="17"/>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A20" s="7" t="s">
         <v>22</v>
       </c>
@@ -6769,7 +6766,7 @@
       <c r="I20" s="5"/>
       <c r="J20" s="5"/>
     </row>
-    <row r="21" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A21" s="7" t="s">
         <v>22</v>
       </c>
@@ -6791,7 +6788,7 @@
       <c r="I21" s="5"/>
       <c r="J21" s="5"/>
     </row>
-    <row r="22" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A22" s="7" t="s">
         <v>22</v>
       </c>
@@ -6813,7 +6810,7 @@
       <c r="I22" s="5"/>
       <c r="J22" s="5"/>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
         <v>19</v>
       </c>
@@ -6839,7 +6836,7 @@
         <v>0.19</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A24" s="7" t="s">
         <v>22</v>
       </c>
@@ -6863,7 +6860,7 @@
       <c r="K24" s="16"/>
       <c r="L24" s="16"/>
     </row>
-    <row r="25" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A25" s="7" t="s">
         <v>22</v>
       </c>
@@ -6887,7 +6884,7 @@
       <c r="K25" s="16"/>
       <c r="L25" s="16"/>
     </row>
-    <row r="26" spans="1:12" ht="51" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:12" ht="52.8" x14ac:dyDescent="0.3">
       <c r="A26" s="7" t="s">
         <v>22</v>
       </c>
@@ -6911,7 +6908,7 @@
       <c r="K26" s="16"/>
       <c r="L26" s="16"/>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A27" s="17" t="s">
         <v>16</v>
       </c>
@@ -6941,7 +6938,7 @@
       <c r="K27" s="17"/>
       <c r="L27" s="17"/>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A28" s="17" t="s">
         <v>19</v>
       </c>
@@ -6971,7 +6968,7 @@
       <c r="K28" s="17"/>
       <c r="L28" s="17"/>
     </row>
-    <row r="29" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:12" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A29" s="7" t="s">
         <v>22</v>
       </c>
@@ -6993,7 +6990,7 @@
       <c r="I29" s="5"/>
       <c r="J29" s="5"/>
     </row>
-    <row r="30" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A30" s="7" t="s">
         <v>22</v>
       </c>
@@ -7015,7 +7012,7 @@
       <c r="I30" s="5"/>
       <c r="J30" s="5"/>
     </row>
-    <row r="31" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:12" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A31" s="7" t="s">
         <v>22</v>
       </c>
@@ -7037,7 +7034,7 @@
       <c r="I31" s="5"/>
       <c r="J31" s="5"/>
     </row>
-    <row r="32" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A32" s="7" t="s">
         <v>22</v>
       </c>
@@ -7059,7 +7056,7 @@
       <c r="I32" s="5"/>
       <c r="J32" s="5"/>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
         <v>19</v>
       </c>
@@ -7085,7 +7082,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="34" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A34" s="7" t="s">
         <v>22</v>
       </c>
@@ -7107,7 +7104,7 @@
       <c r="I34" s="5"/>
       <c r="J34" s="5"/>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A35" s="7" t="s">
         <v>22</v>
       </c>
@@ -7129,7 +7126,7 @@
       <c r="I35" s="5"/>
       <c r="J35" s="5"/>
     </row>
-    <row r="36" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:12" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A36" s="7" t="s">
         <v>22</v>
       </c>
@@ -7151,7 +7148,7 @@
       <c r="I36" s="5"/>
       <c r="J36" s="5"/>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
         <v>19</v>
       </c>
@@ -7177,7 +7174,7 @@
         <v>0.56000000000000005</v>
       </c>
     </row>
-    <row r="38" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:12" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A38" s="7" t="s">
         <v>22</v>
       </c>
@@ -7199,7 +7196,7 @@
       <c r="I38" s="5"/>
       <c r="J38" s="5"/>
     </row>
-    <row r="39" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A39" s="7" t="s">
         <v>22</v>
       </c>
@@ -7221,7 +7218,7 @@
       <c r="I39" s="5"/>
       <c r="J39" s="5"/>
     </row>
-    <row r="40" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A40" s="17" t="s">
         <v>19</v>
       </c>
@@ -7251,7 +7248,7 @@
       <c r="K40" s="17"/>
       <c r="L40" s="17"/>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A41" s="7" t="s">
         <v>22</v>
       </c>
@@ -7273,7 +7270,7 @@
       <c r="I41" s="5"/>
       <c r="J41" s="5"/>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A42" s="7" t="s">
         <v>22</v>
       </c>
@@ -7295,7 +7292,7 @@
       <c r="I42" s="5"/>
       <c r="J42" s="5"/>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A43" s="7" t="s">
         <v>22</v>
       </c>
@@ -7317,7 +7314,7 @@
       <c r="I43" s="5"/>
       <c r="J43" s="5"/>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A44" s="7" t="s">
         <v>22</v>
       </c>
@@ -7339,7 +7336,7 @@
       <c r="I44" s="5"/>
       <c r="J44" s="5"/>
     </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A45" s="7" t="s">
         <v>22</v>
       </c>
@@ -7361,7 +7358,7 @@
       <c r="I45" s="5"/>
       <c r="J45" s="5"/>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
         <v>16</v>
       </c>
@@ -7387,7 +7384,7 @@
         <v>0.46</v>
       </c>
     </row>
-    <row r="47" spans="1:12" ht="51" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:12" ht="52.8" x14ac:dyDescent="0.3">
       <c r="A47" s="17" t="s">
         <v>19</v>
       </c>
@@ -7417,7 +7414,7 @@
       <c r="K47" s="17"/>
       <c r="L47" s="17"/>
     </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A48" s="7" t="s">
         <v>22</v>
       </c>
@@ -7439,7 +7436,7 @@
       <c r="I48" s="5"/>
       <c r="J48" s="5"/>
     </row>
-    <row r="49" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:12" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A49" s="7" t="s">
         <v>22</v>
       </c>
@@ -7461,7 +7458,7 @@
       <c r="I49" s="5"/>
       <c r="J49" s="5"/>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A50" s="7" t="s">
         <v>22</v>
       </c>
@@ -7483,7 +7480,7 @@
       <c r="I50" s="5"/>
       <c r="J50" s="5"/>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A51" s="17" t="s">
         <v>16</v>
       </c>
@@ -7511,7 +7508,7 @@
         <v>1.36</v>
       </c>
     </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A52" s="17" t="s">
         <v>19</v>
       </c>
@@ -7539,7 +7536,7 @@
         <v>0.52</v>
       </c>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A53" s="7" t="s">
         <v>22</v>
       </c>
@@ -7561,7 +7558,7 @@
       <c r="I53" s="5"/>
       <c r="J53" s="5"/>
     </row>
-    <row r="54" spans="1:12" ht="114.75" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:12" ht="118.8" x14ac:dyDescent="0.3">
       <c r="A54" s="7" t="s">
         <v>22</v>
       </c>
@@ -7583,7 +7580,7 @@
       <c r="I54" s="5"/>
       <c r="J54" s="5"/>
     </row>
-    <row r="55" spans="1:12" ht="51" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:12" ht="52.8" x14ac:dyDescent="0.3">
       <c r="A55" s="7" t="s">
         <v>22</v>
       </c>
@@ -7605,7 +7602,7 @@
       <c r="I55" s="5"/>
       <c r="J55" s="5"/>
     </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
         <v>19</v>
       </c>
@@ -7631,7 +7628,7 @@
         <v>0.36</v>
       </c>
     </row>
-    <row r="57" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A57" s="7" t="s">
         <v>22</v>
       </c>
@@ -7655,7 +7652,7 @@
       <c r="K57" s="17"/>
       <c r="L57" s="17"/>
     </row>
-    <row r="58" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:12" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A58" s="7" t="s">
         <v>22</v>
       </c>
@@ -7679,7 +7676,7 @@
       <c r="K58" s="17"/>
       <c r="L58" s="17"/>
     </row>
-    <row r="59" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A59" s="7" t="s">
         <v>22</v>
       </c>
@@ -7703,7 +7700,7 @@
       <c r="K59" s="17"/>
       <c r="L59" s="17"/>
     </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
         <v>19</v>
       </c>
@@ -7729,7 +7726,7 @@
         <v>0.28000000000000003</v>
       </c>
     </row>
-    <row r="61" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A61" s="24" t="s">
         <v>22</v>
       </c>
@@ -7753,7 +7750,7 @@
       <c r="K61" s="17"/>
       <c r="L61" s="17"/>
     </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
         <v>19</v>
       </c>
@@ -7779,7 +7776,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="63" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:12" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A63" s="7" t="s">
         <v>22</v>
       </c>
@@ -7803,7 +7800,7 @@
       <c r="K63" s="16"/>
       <c r="L63" s="16"/>
     </row>
-    <row r="64" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A64" s="7" t="s">
         <v>22</v>
       </c>
@@ -7827,7 +7824,7 @@
       <c r="K64" s="16"/>
       <c r="L64" s="16"/>
     </row>
-    <row r="65" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A65" s="7" t="s">
         <v>22</v>
       </c>
@@ -7851,7 +7848,7 @@
       <c r="K65" s="16"/>
       <c r="L65" s="16"/>
     </row>
-    <row r="66" spans="1:12" ht="51" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:12" ht="52.8" x14ac:dyDescent="0.3">
       <c r="A66" s="7" t="s">
         <v>22</v>
       </c>
@@ -7875,7 +7872,7 @@
       <c r="K66" s="16"/>
       <c r="L66" s="16"/>
     </row>
-    <row r="67" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
         <v>16</v>
       </c>
@@ -7901,7 +7898,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="68" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="s">
         <v>19</v>
       </c>
@@ -7927,7 +7924,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="69" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A69" s="7" t="s">
         <v>22</v>
       </c>
@@ -7951,7 +7948,7 @@
       <c r="K69" s="16"/>
       <c r="L69" s="16"/>
     </row>
-    <row r="70" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:12" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A70" s="7" t="s">
         <v>22</v>
       </c>
@@ -7975,7 +7972,7 @@
       <c r="K70" s="16"/>
       <c r="L70" s="16"/>
     </row>
-    <row r="71" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A71" s="1" t="s">
         <v>19</v>
       </c>
@@ -8001,7 +7998,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="72" spans="1:12" ht="63.75" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:12" ht="66" x14ac:dyDescent="0.3">
       <c r="A72" s="7" t="s">
         <v>22</v>
       </c>
@@ -8025,7 +8022,7 @@
       <c r="K72" s="16"/>
       <c r="L72" s="16"/>
     </row>
-    <row r="73" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A73" s="1" t="s">
         <v>19</v>
       </c>
@@ -8051,7 +8048,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="74" spans="1:12" ht="63.75" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:12" ht="66" x14ac:dyDescent="0.3">
       <c r="A74" s="7" t="s">
         <v>22</v>
       </c>
@@ -8075,7 +8072,7 @@
       <c r="K74" s="16"/>
       <c r="L74" s="16"/>
     </row>
-    <row r="75" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A75" s="7" t="s">
         <v>22</v>
       </c>
@@ -8099,7 +8096,7 @@
       <c r="K75" s="16"/>
       <c r="L75" s="16"/>
     </row>
-    <row r="76" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A76" s="1" t="s">
         <v>16</v>
       </c>
@@ -8125,7 +8122,7 @@
         <v>0.91</v>
       </c>
     </row>
-    <row r="77" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A77" s="1" t="s">
         <v>19</v>
       </c>
@@ -8151,7 +8148,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="78" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A78" s="7" t="s">
         <v>22</v>
       </c>
@@ -8175,7 +8172,7 @@
       <c r="K78" s="16"/>
       <c r="L78" s="16"/>
     </row>
-    <row r="79" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A79" s="1" t="s">
         <v>19</v>
       </c>
@@ -8201,7 +8198,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="80" spans="1:12" ht="51" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:12" ht="52.8" x14ac:dyDescent="0.3">
       <c r="A80" s="7" t="s">
         <v>22</v>
       </c>
@@ -8225,7 +8222,7 @@
       <c r="K80" s="16"/>
       <c r="L80" s="16"/>
     </row>
-    <row r="81" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A81" s="1" t="s">
         <v>19</v>
       </c>
@@ -8251,7 +8248,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="82" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A82" s="7" t="s">
         <v>22</v>
       </c>
@@ -8275,7 +8272,7 @@
       <c r="K82" s="16"/>
       <c r="L82" s="16"/>
     </row>
-    <row r="83" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A83" s="1" t="s">
         <v>19</v>
       </c>
@@ -8301,7 +8298,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="84" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A84" s="7" t="s">
         <v>22</v>
       </c>
@@ -8325,7 +8322,7 @@
       <c r="K84" s="16"/>
       <c r="L84" s="16"/>
     </row>
-    <row r="85" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A85" s="1" t="s">
         <v>19</v>
       </c>
@@ -8351,7 +8348,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="86" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A86" s="29" t="s">
         <v>22</v>
       </c>
@@ -8375,7 +8372,7 @@
       <c r="K86" s="11"/>
       <c r="L86" s="11"/>
     </row>
-    <row r="87" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A87" s="1" t="s">
         <v>19</v>
       </c>
@@ -8401,7 +8398,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="88" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A88" s="29" t="s">
         <v>22</v>
       </c>
@@ -8425,7 +8422,7 @@
       <c r="K88" s="11"/>
       <c r="L88" s="11"/>
     </row>
-    <row r="89" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A89" s="1" t="s">
         <v>19</v>
       </c>
@@ -8451,7 +8448,7 @@
         <v>0.68</v>
       </c>
     </row>
-    <row r="90" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A90" s="29" t="s">
         <v>22</v>
       </c>
@@ -8475,7 +8472,7 @@
       <c r="K90" s="11"/>
       <c r="L90" s="11"/>
     </row>
-    <row r="91" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A91" s="29" t="s">
         <v>22</v>
       </c>
@@ -8499,7 +8496,7 @@
       <c r="K91" s="11"/>
       <c r="L91" s="11"/>
     </row>
-    <row r="92" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A92" s="29" t="s">
         <v>22</v>
       </c>
@@ -8523,7 +8520,7 @@
       <c r="K92" s="11"/>
       <c r="L92" s="11"/>
     </row>
-    <row r="93" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A93" s="29" t="s">
         <v>22</v>
       </c>
@@ -8547,7 +8544,7 @@
       <c r="K93" s="11"/>
       <c r="L93" s="11"/>
     </row>
-    <row r="94" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A94" s="29" t="s">
         <v>22</v>
       </c>
@@ -8571,7 +8568,7 @@
       <c r="K94" s="11"/>
       <c r="L94" s="11"/>
     </row>
-    <row r="95" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A95" s="29" t="s">
         <v>22</v>
       </c>
@@ -8595,7 +8592,7 @@
       <c r="K95" s="11"/>
       <c r="L95" s="11"/>
     </row>
-    <row r="96" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A96" s="29" t="s">
         <v>22</v>
       </c>
@@ -8619,7 +8616,7 @@
       <c r="K96" s="11"/>
       <c r="L96" s="11"/>
     </row>
-    <row r="97" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A97" s="29" t="s">
         <v>22</v>
       </c>
@@ -8643,7 +8640,7 @@
       <c r="K97" s="11"/>
       <c r="L97" s="11"/>
     </row>
-    <row r="98" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A98" s="29" t="s">
         <v>22</v>
       </c>
@@ -8667,7 +8664,7 @@
       <c r="K98" s="11"/>
       <c r="L98" s="11"/>
     </row>
-    <row r="99" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A99" s="29" t="s">
         <v>22</v>
       </c>
@@ -8691,7 +8688,7 @@
       <c r="K99" s="11"/>
       <c r="L99" s="11"/>
     </row>
-    <row r="100" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A100" s="29" t="s">
         <v>22</v>
       </c>
@@ -8715,7 +8712,7 @@
       <c r="K100" s="11"/>
       <c r="L100" s="11"/>
     </row>
-    <row r="101" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A101" s="29" t="s">
         <v>22</v>
       </c>
@@ -8739,7 +8736,7 @@
       <c r="K101" s="11"/>
       <c r="L101" s="11"/>
     </row>
-    <row r="102" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A102" s="1" t="s">
         <v>16</v>
       </c>
@@ -8765,7 +8762,7 @@
         <v>0.85</v>
       </c>
     </row>
-    <row r="103" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A103" s="1" t="s">
         <v>19</v>
       </c>
@@ -8791,7 +8788,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="104" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A104" s="7" t="s">
         <v>22</v>
       </c>
@@ -8815,7 +8812,7 @@
       <c r="K104" s="16"/>
       <c r="L104" s="16"/>
     </row>
-    <row r="105" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A105" s="7" t="s">
         <v>22</v>
       </c>
@@ -8839,7 +8836,7 @@
       <c r="K105" s="16"/>
       <c r="L105" s="16"/>
     </row>
-    <row r="106" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A106" s="7" t="s">
         <v>22</v>
       </c>
@@ -8863,7 +8860,7 @@
       <c r="K106" s="16"/>
       <c r="L106" s="16"/>
     </row>
-    <row r="107" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A107" s="1" t="s">
         <v>19</v>
       </c>
@@ -8889,7 +8886,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="108" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A108" s="7" t="s">
         <v>22</v>
       </c>
@@ -8913,7 +8910,7 @@
       <c r="K108" s="16"/>
       <c r="L108" s="16"/>
     </row>
-    <row r="109" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A109" s="7" t="s">
         <v>22</v>
       </c>
@@ -8937,7 +8934,7 @@
       <c r="K109" s="16"/>
       <c r="L109" s="16"/>
     </row>
-    <row r="110" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A110" s="1" t="s">
         <v>19</v>
       </c>
@@ -8963,7 +8960,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="111" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A111" s="7" t="s">
         <v>22</v>
       </c>
@@ -8987,7 +8984,7 @@
       <c r="K111" s="16"/>
       <c r="L111" s="16"/>
     </row>
-    <row r="112" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A112" s="1" t="s">
         <v>19</v>
       </c>
@@ -9013,7 +9010,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="113" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A113" s="7" t="s">
         <v>22</v>
       </c>
@@ -9037,7 +9034,7 @@
       <c r="K113" s="16"/>
       <c r="L113" s="16"/>
     </row>
-    <row r="114" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A114" s="7" t="s">
         <v>22</v>
       </c>
@@ -9061,7 +9058,7 @@
       <c r="K114" s="16"/>
       <c r="L114" s="16"/>
     </row>
-    <row r="115" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A115" s="1" t="s">
         <v>19</v>
       </c>
@@ -9087,7 +9084,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="116" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A116" s="7" t="s">
         <v>22</v>
       </c>
@@ -9111,7 +9108,7 @@
       <c r="K116" s="16"/>
       <c r="L116" s="16"/>
     </row>
-    <row r="117" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A117" s="1" t="s">
         <v>19</v>
       </c>
@@ -9137,7 +9134,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="118" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A118" s="7" t="s">
         <v>22</v>
       </c>
@@ -9161,7 +9158,7 @@
       <c r="K118" s="16"/>
       <c r="L118" s="16"/>
     </row>
-    <row r="119" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A119" s="7" t="s">
         <v>22</v>
       </c>
@@ -9185,7 +9182,7 @@
       <c r="K119" s="16"/>
       <c r="L119" s="16"/>
     </row>
-    <row r="120" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A120" s="1" t="s">
         <v>19</v>
       </c>
@@ -9211,7 +9208,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="121" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A121" s="7" t="s">
         <v>22</v>
       </c>
@@ -9235,7 +9232,7 @@
       <c r="K121" s="16"/>
       <c r="L121" s="16"/>
     </row>
-    <row r="122" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A122" s="7" t="s">
         <v>22</v>
       </c>
@@ -9259,7 +9256,7 @@
       <c r="K122" s="16"/>
       <c r="L122" s="16"/>
     </row>
-    <row r="123" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A123" s="1" t="s">
         <v>19</v>
       </c>
@@ -9285,7 +9282,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="124" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A124" s="7" t="s">
         <v>22</v>
       </c>
@@ -9309,7 +9306,7 @@
       <c r="K124" s="16"/>
       <c r="L124" s="16"/>
     </row>
-    <row r="125" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A125" s="1" t="s">
         <v>19</v>
       </c>
@@ -9335,7 +9332,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="126" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A126" s="7" t="s">
         <v>22</v>
       </c>
@@ -9359,7 +9356,7 @@
       <c r="K126" s="16"/>
       <c r="L126" s="16"/>
     </row>
-    <row r="127" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A127" s="7" t="s">
         <v>22</v>
       </c>
@@ -9383,7 +9380,7 @@
       <c r="K127" s="16"/>
       <c r="L127" s="16"/>
     </row>
-    <row r="128" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A128" s="1" t="s">
         <v>19</v>
       </c>
@@ -9409,7 +9406,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="129" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A129" s="7" t="s">
         <v>22</v>
       </c>
@@ -9433,7 +9430,7 @@
       <c r="K129" s="16"/>
       <c r="L129" s="16"/>
     </row>
-    <row r="130" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A130" s="1" t="s">
         <v>19</v>
       </c>
@@ -9459,7 +9456,7 @@
         <v>0.23</v>
       </c>
     </row>
-    <row r="131" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A131" s="7" t="s">
         <v>22</v>
       </c>
@@ -9483,7 +9480,7 @@
       <c r="K131" s="16"/>
       <c r="L131" s="16"/>
     </row>
-    <row r="132" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A132" s="7" t="s">
         <v>22</v>
       </c>
@@ -9507,7 +9504,7 @@
       <c r="K132" s="16"/>
       <c r="L132" s="16"/>
     </row>
-    <row r="133" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A133" s="7" t="s">
         <v>22</v>
       </c>
@@ -9531,7 +9528,7 @@
       <c r="K133" s="16"/>
       <c r="L133" s="16"/>
     </row>
-    <row r="134" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A134" s="7" t="s">
         <v>22</v>
       </c>
@@ -9555,7 +9552,7 @@
       <c r="K134" s="16"/>
       <c r="L134" s="16"/>
     </row>
-    <row r="135" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A135" s="7" t="s">
         <v>22</v>
       </c>
@@ -9579,7 +9576,7 @@
       <c r="K135" s="16"/>
       <c r="L135" s="16"/>
     </row>
-    <row r="136" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:12" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A136" s="7" t="s">
         <v>22</v>
       </c>
@@ -9603,7 +9600,7 @@
       <c r="K136" s="16"/>
       <c r="L136" s="16"/>
     </row>
-    <row r="137" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A137" s="7" t="s">
         <v>22</v>
       </c>
@@ -9627,7 +9624,7 @@
       <c r="K137" s="16"/>
       <c r="L137" s="16"/>
     </row>
-    <row r="138" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A138" s="7" t="s">
         <v>22</v>
       </c>
@@ -9651,7 +9648,7 @@
       <c r="K138" s="16"/>
       <c r="L138" s="16"/>
     </row>
-    <row r="139" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A139" s="1" t="s">
         <v>16</v>
       </c>
@@ -9677,7 +9674,7 @@
         <v>0.28999999999999998</v>
       </c>
     </row>
-    <row r="140" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A140" s="1" t="s">
         <v>19</v>
       </c>
@@ -9703,7 +9700,7 @@
         <v>0.11</v>
       </c>
     </row>
-    <row r="141" spans="1:12" ht="51" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:12" ht="52.8" x14ac:dyDescent="0.3">
       <c r="A141" s="7" t="s">
         <v>22</v>
       </c>
@@ -9727,7 +9724,7 @@
       <c r="K141" s="16"/>
       <c r="L141" s="16"/>
     </row>
-    <row r="142" spans="1:12" ht="51" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:12" ht="52.8" x14ac:dyDescent="0.3">
       <c r="A142" s="7" t="s">
         <v>22</v>
       </c>
@@ -9751,7 +9748,7 @@
       <c r="K142" s="16"/>
       <c r="L142" s="16"/>
     </row>
-    <row r="143" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A143" s="1" t="s">
         <v>19</v>
       </c>
@@ -9777,7 +9774,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="144" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A144" s="7" t="s">
         <v>22</v>
       </c>
@@ -9801,7 +9798,7 @@
       <c r="K144" s="16"/>
       <c r="L144" s="16"/>
     </row>
-    <row r="145" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A145" s="1" t="s">
         <v>19</v>
       </c>
@@ -9827,7 +9824,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="146" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A146" s="7" t="s">
         <v>22</v>
       </c>
@@ -9851,7 +9848,7 @@
       <c r="K146" s="16"/>
       <c r="L146" s="16"/>
     </row>
-    <row r="147" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:12" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A147" s="7" t="s">
         <v>22</v>
       </c>
@@ -9875,7 +9872,7 @@
       <c r="K147" s="16"/>
       <c r="L147" s="16"/>
     </row>
-    <row r="148" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A148" s="7" t="s">
         <v>22</v>
       </c>
@@ -9899,7 +9896,7 @@
       <c r="K148" s="16"/>
       <c r="L148" s="16"/>
     </row>
-    <row r="149" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:12" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A149" s="7" t="s">
         <v>22</v>
       </c>
@@ -9923,7 +9920,7 @@
       <c r="K149" s="16"/>
       <c r="L149" s="16"/>
     </row>
-    <row r="150" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A150" s="1" t="s">
         <v>19</v>
       </c>
@@ -9949,7 +9946,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="151" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A151" s="7" t="s">
         <v>22</v>
       </c>
@@ -9973,7 +9970,7 @@
       <c r="K151" s="16"/>
       <c r="L151" s="16"/>
     </row>
-    <row r="152" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A152" s="1" t="s">
         <v>19</v>
       </c>
@@ -9999,7 +9996,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="153" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A153" s="7" t="s">
         <v>22</v>
       </c>
@@ -10023,7 +10020,7 @@
       <c r="K153" s="16"/>
       <c r="L153" s="16"/>
     </row>
-    <row r="154" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A154" s="1" t="s">
         <v>19</v>
       </c>
@@ -10049,7 +10046,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="155" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A155" s="7" t="s">
         <v>22</v>
       </c>
@@ -10073,7 +10070,7 @@
       <c r="K155" s="16"/>
       <c r="L155" s="16"/>
     </row>
-    <row r="156" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A156" s="1" t="s">
         <v>16</v>
       </c>
@@ -10099,7 +10096,7 @@
         <v>0.41</v>
       </c>
     </row>
-    <row r="157" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A157" s="1" t="s">
         <v>19</v>
       </c>
@@ -10125,7 +10122,7 @@
         <v>0.13</v>
       </c>
     </row>
-    <row r="158" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A158" s="7" t="s">
         <v>22</v>
       </c>
@@ -10149,7 +10146,7 @@
       <c r="K158" s="16"/>
       <c r="L158" s="16"/>
     </row>
-    <row r="159" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A159" s="7" t="s">
         <v>22</v>
       </c>
@@ -10173,7 +10170,7 @@
       <c r="K159" s="16"/>
       <c r="L159" s="16"/>
     </row>
-    <row r="160" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A160" s="7" t="s">
         <v>22</v>
       </c>
@@ -10197,7 +10194,7 @@
       <c r="K160" s="16"/>
       <c r="L160" s="16"/>
     </row>
-    <row r="161" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A161" s="7" t="s">
         <v>22</v>
       </c>
@@ -10221,7 +10218,7 @@
       <c r="K161" s="16"/>
       <c r="L161" s="16"/>
     </row>
-    <row r="162" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A162" s="1" t="s">
         <v>19</v>
       </c>
@@ -10247,7 +10244,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="163" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:12" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A163" s="7" t="s">
         <v>22</v>
       </c>
@@ -10271,7 +10268,7 @@
       <c r="K163" s="16"/>
       <c r="L163" s="16"/>
     </row>
-    <row r="164" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A164" s="1" t="s">
         <v>19</v>
       </c>
@@ -10297,7 +10294,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="165" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A165" s="7" t="s">
         <v>22</v>
       </c>
@@ -10321,7 +10318,7 @@
       <c r="K165" s="16"/>
       <c r="L165" s="16"/>
     </row>
-    <row r="166" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:12" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A166" s="7" t="s">
         <v>22</v>
       </c>
@@ -10345,7 +10342,7 @@
       <c r="K166" s="16"/>
       <c r="L166" s="16"/>
     </row>
-    <row r="167" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A167" s="1" t="s">
         <v>19</v>
       </c>
@@ -10371,7 +10368,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="168" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:12" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A168" s="7" t="s">
         <v>22</v>
       </c>
@@ -10395,7 +10392,7 @@
       <c r="K168" s="16"/>
       <c r="L168" s="16"/>
     </row>
-    <row r="169" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A169" s="1" t="s">
         <v>19</v>
       </c>
@@ -10421,7 +10418,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="170" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A170" s="7" t="s">
         <v>22</v>
       </c>
@@ -10445,7 +10442,7 @@
       <c r="K170" s="16"/>
       <c r="L170" s="16"/>
     </row>
-    <row r="171" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A171" s="7" t="s">
         <v>22</v>
       </c>
@@ -10469,7 +10466,7 @@
       <c r="K171" s="16"/>
       <c r="L171" s="16"/>
     </row>
-    <row r="172" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A172" s="7" t="s">
         <v>22</v>
       </c>
@@ -10493,7 +10490,7 @@
       <c r="K172" s="16"/>
       <c r="L172" s="16"/>
     </row>
-    <row r="173" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A173" s="1" t="s">
         <v>19</v>
       </c>
@@ -10519,7 +10516,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="174" spans="1:12" ht="63.75" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:12" ht="66" x14ac:dyDescent="0.3">
       <c r="A174" s="7" t="s">
         <v>22</v>
       </c>
@@ -10543,7 +10540,7 @@
       <c r="K174" s="16"/>
       <c r="L174" s="16"/>
     </row>
-    <row r="175" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A175" s="1" t="s">
         <v>19</v>
       </c>
@@ -10569,7 +10566,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="176" spans="1:12" ht="51" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:12" ht="52.8" x14ac:dyDescent="0.3">
       <c r="A176" s="7" t="s">
         <v>22</v>
       </c>
@@ -10593,7 +10590,7 @@
       <c r="K176" s="16"/>
       <c r="L176" s="16"/>
     </row>
-    <row r="177" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A177" s="1" t="s">
         <v>13</v>
       </c>
@@ -10619,7 +10616,7 @@
         <v>0.64</v>
       </c>
     </row>
-    <row r="178" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A178" s="1" t="s">
         <v>16</v>
       </c>
@@ -10645,7 +10642,7 @@
         <v>0.26</v>
       </c>
     </row>
-    <row r="179" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A179" s="1" t="s">
         <v>19</v>
       </c>
@@ -10671,7 +10668,7 @@
         <v>0.13</v>
       </c>
     </row>
-    <row r="180" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:12" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A180" s="7" t="s">
         <v>22</v>
       </c>
@@ -10695,7 +10692,7 @@
       <c r="K180" s="16"/>
       <c r="L180" s="16"/>
     </row>
-    <row r="181" spans="1:12" ht="63.75" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:12" ht="66" x14ac:dyDescent="0.3">
       <c r="A181" s="7" t="s">
         <v>22</v>
       </c>
@@ -10719,7 +10716,7 @@
       <c r="K181" s="16"/>
       <c r="L181" s="16"/>
     </row>
-    <row r="182" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A182" s="1" t="s">
         <v>19</v>
       </c>
@@ -10745,7 +10742,7 @@
         <v>0.11</v>
       </c>
     </row>
-    <row r="183" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A183" s="7" t="s">
         <v>22</v>
       </c>
@@ -10769,7 +10766,7 @@
       <c r="K183" s="16"/>
       <c r="L183" s="16"/>
     </row>
-    <row r="184" spans="1:12" ht="89.25" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:12" ht="92.4" x14ac:dyDescent="0.3">
       <c r="A184" s="7" t="s">
         <v>22</v>
       </c>
@@ -10793,7 +10790,7 @@
       <c r="K184" s="16"/>
       <c r="L184" s="16"/>
     </row>
-    <row r="185" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A185" s="1" t="s">
         <v>19</v>
       </c>
@@ -10819,7 +10816,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="186" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:12" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A186" s="7" t="s">
         <v>22</v>
       </c>
@@ -10843,7 +10840,7 @@
       <c r="K186" s="16"/>
       <c r="L186" s="16"/>
     </row>
-    <row r="187" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A187" s="1" t="s">
         <v>16</v>
       </c>
@@ -10869,7 +10866,7 @@
         <v>0.38</v>
       </c>
     </row>
-    <row r="188" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A188" s="1" t="s">
         <v>19</v>
       </c>
@@ -10895,7 +10892,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="189" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A189" s="7" t="s">
         <v>22</v>
       </c>
@@ -10919,7 +10916,7 @@
       <c r="K189" s="16"/>
       <c r="L189" s="16"/>
     </row>
-    <row r="190" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A190" s="1" t="s">
         <v>19</v>
       </c>
@@ -10945,7 +10942,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="191" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A191" s="7" t="s">
         <v>22</v>
       </c>
@@ -10969,7 +10966,7 @@
       <c r="K191" s="16"/>
       <c r="L191" s="16"/>
     </row>
-    <row r="192" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A192" s="1" t="s">
         <v>19</v>
       </c>
@@ -10995,7 +10992,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="193" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A193" s="7" t="s">
         <v>22</v>
       </c>
@@ -11019,7 +11016,7 @@
       <c r="K193" s="16"/>
       <c r="L193" s="16"/>
     </row>
-    <row r="194" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A194" s="1" t="s">
         <v>19</v>
       </c>
@@ -11045,7 +11042,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="195" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:12" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A195" s="7" t="s">
         <v>22</v>
       </c>
@@ -11069,7 +11066,7 @@
       <c r="K195" s="16"/>
       <c r="L195" s="16"/>
     </row>
-    <row r="196" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A196" s="1" t="s">
         <v>19</v>
       </c>
@@ -11095,7 +11092,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="197" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:12" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A197" s="7" t="s">
         <v>22</v>
       </c>
@@ -11119,7 +11116,7 @@
       <c r="K197" s="16"/>
       <c r="L197" s="16"/>
     </row>
-    <row r="198" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A198" s="7" t="s">
         <v>22</v>
       </c>
@@ -11143,7 +11140,7 @@
       <c r="K198" s="16"/>
       <c r="L198" s="16"/>
     </row>
-    <row r="199" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A199" s="1" t="s">
         <v>10</v>
       </c>
@@ -11169,7 +11166,7 @@
         <v>1.53</v>
       </c>
     </row>
-    <row r="200" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A200" s="1" t="s">
         <v>13</v>
       </c>
@@ -11195,7 +11192,7 @@
         <v>1.49</v>
       </c>
     </row>
-    <row r="201" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A201" s="1" t="s">
         <v>16</v>
       </c>
@@ -11221,7 +11218,7 @@
         <v>0.43</v>
       </c>
     </row>
-    <row r="202" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A202" s="1" t="s">
         <v>19</v>
       </c>
@@ -11247,7 +11244,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="203" spans="1:12" ht="63.75" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:12" ht="66" x14ac:dyDescent="0.3">
       <c r="A203" s="7" t="s">
         <v>22</v>
       </c>
@@ -11271,7 +11268,7 @@
       <c r="K203" s="16"/>
       <c r="L203" s="16"/>
     </row>
-    <row r="204" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A204" s="1" t="s">
         <v>19</v>
       </c>
@@ -11297,7 +11294,7 @@
         <v>0.33</v>
       </c>
     </row>
-    <row r="205" spans="1:12" ht="63.75" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:12" ht="66" x14ac:dyDescent="0.3">
       <c r="A205" s="7" t="s">
         <v>22</v>
       </c>
@@ -11321,7 +11318,7 @@
       <c r="K205" s="16"/>
       <c r="L205" s="16"/>
     </row>
-    <row r="206" spans="1:12" ht="51" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:12" ht="52.8" x14ac:dyDescent="0.3">
       <c r="A206" s="7" t="s">
         <v>22</v>
       </c>
@@ -11345,7 +11342,7 @@
       <c r="K206" s="16"/>
       <c r="L206" s="16"/>
     </row>
-    <row r="207" spans="1:12" ht="76.5" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:12" ht="79.2" x14ac:dyDescent="0.3">
       <c r="A207" s="7" t="s">
         <v>22</v>
       </c>
@@ -11369,7 +11366,7 @@
       <c r="K207" s="16"/>
       <c r="L207" s="16"/>
     </row>
-    <row r="208" spans="1:12" ht="63.75" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:12" ht="66" x14ac:dyDescent="0.3">
       <c r="A208" s="7" t="s">
         <v>22</v>
       </c>
@@ -11393,7 +11390,7 @@
       <c r="K208" s="16"/>
       <c r="L208" s="16"/>
     </row>
-    <row r="209" spans="1:12" ht="63.75" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:12" ht="66" x14ac:dyDescent="0.3">
       <c r="A209" s="7" t="s">
         <v>22</v>
       </c>
@@ -11417,7 +11414,7 @@
       <c r="K209" s="16"/>
       <c r="L209" s="16"/>
     </row>
-    <row r="210" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A210" s="1" t="s">
         <v>16</v>
       </c>
@@ -11443,7 +11440,7 @@
         <v>0.11</v>
       </c>
     </row>
-    <row r="211" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A211" s="1" t="s">
         <v>19</v>
       </c>
@@ -11469,7 +11466,7 @@
         <v>0.11</v>
       </c>
     </row>
-    <row r="212" spans="1:12" ht="102" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:12" ht="105.6" x14ac:dyDescent="0.3">
       <c r="A212" s="7" t="s">
         <v>22</v>
       </c>
@@ -11493,7 +11490,7 @@
       <c r="K212" s="16"/>
       <c r="L212" s="16"/>
     </row>
-    <row r="213" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A213" s="1" t="s">
         <v>16</v>
       </c>
@@ -11519,7 +11516,7 @@
         <v>0.95</v>
       </c>
     </row>
-    <row r="214" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A214" s="1" t="s">
         <v>19</v>
       </c>
@@ -11545,7 +11542,7 @@
         <v>0.95</v>
       </c>
     </row>
-    <row r="215" spans="1:12" ht="102" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:12" ht="105.6" x14ac:dyDescent="0.3">
       <c r="A215" s="7" t="s">
         <v>22</v>
       </c>
@@ -11569,7 +11566,7 @@
       <c r="K215" s="16"/>
       <c r="L215" s="16"/>
     </row>
-    <row r="216" spans="1:12" ht="102" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:12" ht="105.6" x14ac:dyDescent="0.3">
       <c r="A216" s="7" t="s">
         <v>22</v>
       </c>
@@ -11593,7 +11590,7 @@
       <c r="K216" s="16"/>
       <c r="L216" s="16"/>
     </row>
-    <row r="217" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A217" s="1" t="s">
         <v>13</v>
       </c>
@@ -11619,7 +11616,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="218" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A218" s="1" t="s">
         <v>16</v>
       </c>
@@ -11645,7 +11642,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="219" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A219" s="1" t="s">
         <v>19</v>
       </c>
@@ -11671,7 +11668,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="220" spans="1:12" ht="76.5" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:12" ht="79.2" x14ac:dyDescent="0.3">
       <c r="A220" s="7" t="s">
         <v>22</v>
       </c>
@@ -11695,7 +11692,7 @@
       <c r="K220" s="16"/>
       <c r="L220" s="16"/>
     </row>
-    <row r="221" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A221" s="1" t="s">
         <v>10</v>
       </c>
@@ -11721,7 +11718,7 @@
         <v>4.49</v>
       </c>
     </row>
-    <row r="222" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A222" s="1" t="s">
         <v>13</v>
       </c>
@@ -11747,7 +11744,7 @@
         <v>3.51</v>
       </c>
     </row>
-    <row r="223" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A223" s="1" t="s">
         <v>16</v>
       </c>
@@ -11773,7 +11770,7 @@
         <v>3.25</v>
       </c>
     </row>
-    <row r="224" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A224" s="1" t="s">
         <v>19</v>
       </c>
@@ -11799,7 +11796,7 @@
         <v>1.42</v>
       </c>
     </row>
-    <row r="225" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:12" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A225" s="7" t="s">
         <v>22</v>
       </c>
@@ -11823,7 +11820,7 @@
       <c r="K225" s="16"/>
       <c r="L225" s="16"/>
     </row>
-    <row r="226" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A226" s="7" t="s">
         <v>22</v>
       </c>
@@ -11847,7 +11844,7 @@
       <c r="K226" s="16"/>
       <c r="L226" s="16"/>
     </row>
-    <row r="227" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A227" s="7" t="s">
         <v>22</v>
       </c>
@@ -11871,7 +11868,7 @@
       <c r="K227" s="16"/>
       <c r="L227" s="16"/>
     </row>
-    <row r="228" spans="1:12" ht="63.75" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:12" ht="66" x14ac:dyDescent="0.3">
       <c r="A228" s="7" t="s">
         <v>22</v>
       </c>
@@ -11895,7 +11892,7 @@
       <c r="K228" s="16"/>
       <c r="L228" s="16"/>
     </row>
-    <row r="229" spans="1:12" ht="63.75" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:12" ht="66" x14ac:dyDescent="0.3">
       <c r="A229" s="7" t="s">
         <v>22</v>
       </c>
@@ -11919,7 +11916,7 @@
       <c r="K229" s="16"/>
       <c r="L229" s="16"/>
     </row>
-    <row r="230" spans="1:12" ht="63.75" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:12" ht="66" x14ac:dyDescent="0.3">
       <c r="A230" s="7" t="s">
         <v>22</v>
       </c>
@@ -11943,7 +11940,7 @@
       <c r="K230" s="16"/>
       <c r="L230" s="16"/>
     </row>
-    <row r="231" spans="1:12" ht="140.25" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:12" ht="145.19999999999999" x14ac:dyDescent="0.3">
       <c r="A231" s="7" t="s">
         <v>22</v>
       </c>
@@ -11967,7 +11964,7 @@
       <c r="K231" s="16"/>
       <c r="L231" s="16"/>
     </row>
-    <row r="232" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A232" s="7" t="s">
         <v>22</v>
       </c>
@@ -11991,7 +11988,7 @@
       <c r="K232" s="16"/>
       <c r="L232" s="16"/>
     </row>
-    <row r="233" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A233" s="1" t="s">
         <v>19</v>
       </c>
@@ -12017,7 +12014,7 @@
         <v>1.34</v>
       </c>
     </row>
-    <row r="234" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:12" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A234" s="7" t="s">
         <v>22</v>
       </c>
@@ -12041,7 +12038,7 @@
       <c r="K234" s="16"/>
       <c r="L234" s="16"/>
     </row>
-    <row r="235" spans="1:12" ht="51" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:12" ht="52.8" x14ac:dyDescent="0.3">
       <c r="A235" s="7" t="s">
         <v>22</v>
       </c>
@@ -12065,7 +12062,7 @@
       <c r="K235" s="16"/>
       <c r="L235" s="16"/>
     </row>
-    <row r="236" spans="1:12" ht="76.5" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:12" ht="79.2" x14ac:dyDescent="0.3">
       <c r="A236" s="7" t="s">
         <v>22</v>
       </c>
@@ -12089,7 +12086,7 @@
       <c r="K236" s="16"/>
       <c r="L236" s="16"/>
     </row>
-    <row r="237" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:12" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A237" s="7" t="s">
         <v>22</v>
       </c>
@@ -12113,7 +12110,7 @@
       <c r="K237" s="16"/>
       <c r="L237" s="16"/>
     </row>
-    <row r="238" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A238" s="7" t="s">
         <v>22</v>
       </c>
@@ -12137,7 +12134,7 @@
       <c r="K238" s="16"/>
       <c r="L238" s="16"/>
     </row>
-    <row r="239" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:12" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A239" s="7" t="s">
         <v>22</v>
       </c>
@@ -12161,7 +12158,7 @@
       <c r="K239" s="16"/>
       <c r="L239" s="16"/>
     </row>
-    <row r="240" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A240" s="7" t="s">
         <v>22</v>
       </c>
@@ -12185,7 +12182,7 @@
       <c r="K240" s="16"/>
       <c r="L240" s="16"/>
     </row>
-    <row r="241" spans="1:12" ht="51" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:12" ht="52.8" x14ac:dyDescent="0.3">
       <c r="A241" s="7" t="s">
         <v>22</v>
       </c>
@@ -12209,7 +12206,7 @@
       <c r="K241" s="16"/>
       <c r="L241" s="16"/>
     </row>
-    <row r="242" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A242" s="1" t="s">
         <v>19</v>
       </c>
@@ -12238,7 +12235,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="243" spans="1:12" ht="51" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:12" ht="52.8" x14ac:dyDescent="0.3">
       <c r="A243" s="7" t="s">
         <v>22</v>
       </c>
@@ -12262,7 +12259,7 @@
       <c r="K243" s="16"/>
       <c r="L243" s="16"/>
     </row>
-    <row r="244" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A244" s="7" t="s">
         <v>22</v>
       </c>
@@ -12286,7 +12283,7 @@
       <c r="K244" s="16"/>
       <c r="L244" s="16"/>
     </row>
-    <row r="245" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:12" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A245" s="7" t="s">
         <v>22</v>
       </c>
@@ -12310,7 +12307,7 @@
       <c r="K245" s="16"/>
       <c r="L245" s="16"/>
     </row>
-    <row r="246" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A246" s="7" t="s">
         <v>22</v>
       </c>
@@ -12334,7 +12331,7 @@
       <c r="K246" s="16"/>
       <c r="L246" s="16"/>
     </row>
-    <row r="247" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A247" s="1" t="s">
         <v>19</v>
       </c>
@@ -12360,7 +12357,7 @@
         <v>0.11</v>
       </c>
     </row>
-    <row r="248" spans="1:12" ht="89.25" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:12" ht="92.4" x14ac:dyDescent="0.3">
       <c r="A248" s="7" t="s">
         <v>22</v>
       </c>
@@ -12384,7 +12381,7 @@
       <c r="K248" s="16"/>
       <c r="L248" s="16"/>
     </row>
-    <row r="249" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A249" s="1" t="s">
         <v>19</v>
       </c>
@@ -12410,7 +12407,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="250" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A250" s="7" t="s">
         <v>22</v>
       </c>
@@ -12434,7 +12431,7 @@
       <c r="K250" s="16"/>
       <c r="L250" s="16"/>
     </row>
-    <row r="251" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:12" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A251" s="7" t="s">
         <v>22</v>
       </c>
@@ -12458,7 +12455,7 @@
       <c r="K251" s="16"/>
       <c r="L251" s="16"/>
     </row>
-    <row r="252" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:12" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A252" s="7" t="s">
         <v>22</v>
       </c>
@@ -12482,7 +12479,7 @@
       <c r="K252" s="16"/>
       <c r="L252" s="16"/>
     </row>
-    <row r="253" spans="1:12" ht="51" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:12" ht="52.8" x14ac:dyDescent="0.3">
       <c r="A253" s="7" t="s">
         <v>22</v>
       </c>
@@ -12506,7 +12503,7 @@
       <c r="K253" s="16"/>
       <c r="L253" s="16"/>
     </row>
-    <row r="254" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:12" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A254" s="7" t="s">
         <v>22</v>
       </c>
@@ -12530,7 +12527,7 @@
       <c r="K254" s="16"/>
       <c r="L254" s="16"/>
     </row>
-    <row r="255" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:12" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A255" s="7" t="s">
         <v>22</v>
       </c>
@@ -12554,7 +12551,7 @@
       <c r="K255" s="16"/>
       <c r="L255" s="16"/>
     </row>
-    <row r="256" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A256" s="7" t="s">
         <v>22</v>
       </c>
@@ -12578,7 +12575,7 @@
       <c r="K256" s="16"/>
       <c r="L256" s="16"/>
     </row>
-    <row r="257" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A257" s="7" t="s">
         <v>22</v>
       </c>
@@ -12602,7 +12599,7 @@
       <c r="K257" s="16"/>
       <c r="L257" s="16"/>
     </row>
-    <row r="258" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:12" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A258" s="7" t="s">
         <v>22</v>
       </c>
@@ -12626,7 +12623,7 @@
       <c r="K258" s="16"/>
       <c r="L258" s="16"/>
     </row>
-    <row r="259" spans="1:12" ht="51" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:12" ht="52.8" x14ac:dyDescent="0.3">
       <c r="A259" s="7" t="s">
         <v>22</v>
       </c>
@@ -12650,7 +12647,7 @@
       <c r="K259" s="16"/>
       <c r="L259" s="16"/>
     </row>
-    <row r="260" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:12" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A260" s="7" t="s">
         <v>22</v>
       </c>
@@ -12674,7 +12671,7 @@
       <c r="K260" s="16"/>
       <c r="L260" s="16"/>
     </row>
-    <row r="261" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:12" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A261" s="7" t="s">
         <v>22</v>
       </c>
@@ -12698,7 +12695,7 @@
       <c r="K261" s="16"/>
       <c r="L261" s="16"/>
     </row>
-    <row r="262" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A262" s="1" t="s">
         <v>16</v>
       </c>
@@ -12724,7 +12721,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="263" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A263" s="1" t="s">
         <v>19</v>
       </c>
@@ -12750,7 +12747,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="264" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A264" s="7" t="s">
         <v>22</v>
       </c>
@@ -12774,7 +12771,7 @@
       <c r="K264" s="16"/>
       <c r="L264" s="16"/>
     </row>
-    <row r="265" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A265" s="7" t="s">
         <v>22</v>
       </c>
@@ -12798,7 +12795,7 @@
       <c r="K265" s="16"/>
       <c r="L265" s="16"/>
     </row>
-    <row r="266" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:12" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A266" s="7" t="s">
         <v>22</v>
       </c>
@@ -12822,7 +12819,7 @@
       <c r="K266" s="16"/>
       <c r="L266" s="16"/>
     </row>
-    <row r="267" spans="1:12" ht="51" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:12" ht="52.8" x14ac:dyDescent="0.3">
       <c r="A267" s="7" t="s">
         <v>22</v>
       </c>
@@ -12846,7 +12843,7 @@
       <c r="K267" s="16"/>
       <c r="L267" s="16"/>
     </row>
-    <row r="268" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A268" s="1" t="s">
         <v>16</v>
       </c>
@@ -12872,7 +12869,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="269" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A269" s="1" t="s">
         <v>19</v>
       </c>
@@ -12898,7 +12895,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="270" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:12" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A270" s="7" t="s">
         <v>22</v>
       </c>
@@ -12922,7 +12919,7 @@
       <c r="K270" s="16"/>
       <c r="L270" s="16"/>
     </row>
-    <row r="271" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A271" s="1" t="s">
         <v>13</v>
       </c>
@@ -12948,7 +12945,7 @@
         <v>0.98</v>
       </c>
     </row>
-    <row r="272" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A272" s="1" t="s">
         <v>16</v>
       </c>
@@ -12974,7 +12971,7 @@
         <v>0.98</v>
       </c>
     </row>
-    <row r="273" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A273" s="1" t="s">
         <v>19</v>
       </c>
@@ -13000,7 +12997,7 @@
         <v>0.47</v>
       </c>
     </row>
-    <row r="274" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:12" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A274" s="7" t="s">
         <v>22</v>
       </c>
@@ -13024,7 +13021,7 @@
       <c r="K274" s="16"/>
       <c r="L274" s="16"/>
     </row>
-    <row r="275" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A275" s="7" t="s">
         <v>22</v>
       </c>
@@ -13048,7 +13045,7 @@
       <c r="K275" s="16"/>
       <c r="L275" s="16"/>
     </row>
-    <row r="276" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A276" s="1" t="s">
         <v>19</v>
       </c>
@@ -13074,7 +13071,7 @@
         <v>0.42</v>
       </c>
     </row>
-    <row r="277" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:12" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A277" s="7" t="s">
         <v>22</v>
       </c>
@@ -13098,7 +13095,7 @@
       <c r="K277" s="16"/>
       <c r="L277" s="16"/>
     </row>
-    <row r="278" spans="1:12" ht="76.5" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:12" ht="79.2" x14ac:dyDescent="0.3">
       <c r="A278" s="7" t="s">
         <v>22</v>
       </c>
@@ -13122,7 +13119,7 @@
       <c r="K278" s="16"/>
       <c r="L278" s="16"/>
     </row>
-    <row r="279" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A279" s="7" t="s">
         <v>22</v>
       </c>
@@ -13146,7 +13143,7 @@
       <c r="K279" s="16"/>
       <c r="L279" s="16"/>
     </row>
-    <row r="280" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A280" s="1" t="s">
         <v>19</v>
       </c>
@@ -13172,7 +13169,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="281" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A281" s="7" t="s">
         <v>22</v>
       </c>
@@ -13196,7 +13193,7 @@
       <c r="K281" s="16"/>
       <c r="L281" s="16"/>
     </row>
-    <row r="282" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A282" s="7" t="s">
         <v>22</v>
       </c>
@@ -13220,7 +13217,7 @@
       <c r="K282" s="16"/>
       <c r="L282" s="16"/>
     </row>
-    <row r="283" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A283" s="7" t="s">
         <v>22</v>
       </c>
@@ -13244,7 +13241,7 @@
       <c r="K283" s="16"/>
       <c r="L283" s="16"/>
     </row>
-    <row r="284" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A284" s="1" t="s">
         <v>10</v>
       </c>
@@ -13270,7 +13267,7 @@
         <v>30.44</v>
       </c>
     </row>
-    <row r="285" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A285" s="1" t="s">
         <v>13</v>
       </c>
@@ -13296,7 +13293,7 @@
         <v>6.4</v>
       </c>
     </row>
-    <row r="286" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A286" s="1" t="s">
         <v>16</v>
       </c>
@@ -13322,7 +13319,7 @@
         <v>6.4</v>
       </c>
     </row>
-    <row r="287" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A287" s="1" t="s">
         <v>19</v>
       </c>
@@ -13348,7 +13345,7 @@
         <v>6.4</v>
       </c>
     </row>
-    <row r="288" spans="1:12" ht="63.75" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:12" ht="66" x14ac:dyDescent="0.3">
       <c r="A288" s="7" t="s">
         <v>22</v>
       </c>
@@ -13372,7 +13369,7 @@
       <c r="K288" s="16"/>
       <c r="L288" s="16"/>
     </row>
-    <row r="289" spans="1:12" ht="63.75" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:12" ht="66" x14ac:dyDescent="0.3">
       <c r="A289" s="7" t="s">
         <v>22</v>
       </c>
@@ -13396,7 +13393,7 @@
       <c r="K289" s="16"/>
       <c r="L289" s="16"/>
     </row>
-    <row r="290" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A290" s="1" t="s">
         <v>13</v>
       </c>
@@ -13422,7 +13419,7 @@
         <v>15.97</v>
       </c>
     </row>
-    <row r="291" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A291" s="1" t="s">
         <v>16</v>
       </c>
@@ -13448,7 +13445,7 @@
         <v>15.97</v>
       </c>
     </row>
-    <row r="292" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A292" s="1" t="s">
         <v>19</v>
       </c>
@@ -13474,7 +13471,7 @@
         <v>15.97</v>
       </c>
     </row>
-    <row r="293" spans="1:12" ht="89.25" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:12" ht="92.4" x14ac:dyDescent="0.3">
       <c r="A293" s="7" t="s">
         <v>22</v>
       </c>
@@ -13498,7 +13495,7 @@
       <c r="K293" s="16"/>
       <c r="L293" s="16"/>
     </row>
-    <row r="294" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A294" s="1" t="s">
         <v>13</v>
       </c>
@@ -13524,7 +13521,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="295" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A295" s="1" t="s">
         <v>16</v>
       </c>
@@ -13550,7 +13547,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="296" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A296" s="1" t="s">
         <v>19</v>
       </c>
@@ -13576,7 +13573,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="297" spans="1:12" ht="89.25" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:12" ht="92.4" x14ac:dyDescent="0.3">
       <c r="A297" s="7" t="s">
         <v>22</v>
       </c>
@@ -13600,7 +13597,7 @@
       <c r="K297" s="16"/>
       <c r="L297" s="16"/>
     </row>
-    <row r="298" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A298" s="1" t="s">
         <v>13</v>
       </c>
@@ -13626,7 +13623,7 @@
         <v>5.26</v>
       </c>
     </row>
-    <row r="299" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A299" s="1" t="s">
         <v>16</v>
       </c>
@@ -13652,7 +13649,7 @@
         <v>1.46</v>
       </c>
     </row>
-    <row r="300" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A300" s="1" t="s">
         <v>19</v>
       </c>
@@ -13678,7 +13675,7 @@
         <v>1.46</v>
       </c>
     </row>
-    <row r="301" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A301" s="7" t="s">
         <v>22</v>
       </c>
@@ -13702,7 +13699,7 @@
       <c r="K301" s="16"/>
       <c r="L301" s="16"/>
     </row>
-    <row r="302" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A302" s="1" t="s">
         <v>16</v>
       </c>
@@ -13728,7 +13725,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="303" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A303" s="1" t="s">
         <v>19</v>
       </c>
@@ -13754,7 +13751,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="304" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A304" s="7" t="s">
         <v>22</v>
       </c>
@@ -13778,7 +13775,7 @@
       <c r="K304" s="16"/>
       <c r="L304" s="16"/>
     </row>
-    <row r="305" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A305" s="1" t="s">
         <v>16</v>
       </c>
@@ -13804,7 +13801,7 @@
         <v>0.36</v>
       </c>
     </row>
-    <row r="306" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A306" s="1" t="s">
         <v>19</v>
       </c>
@@ -13830,7 +13827,7 @@
         <v>0.36</v>
       </c>
     </row>
-    <row r="307" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A307" s="33" t="s">
         <v>22</v>
       </c>
@@ -13852,7 +13849,7 @@
       <c r="I307" s="5"/>
       <c r="J307" s="5"/>
     </row>
-    <row r="308" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A308" s="1" t="s">
         <v>16</v>
       </c>
@@ -13878,7 +13875,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="309" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A309" s="1" t="s">
         <v>19</v>
       </c>
@@ -13904,7 +13901,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="310" spans="1:12" ht="51" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:12" ht="52.8" x14ac:dyDescent="0.3">
       <c r="A310" s="7" t="s">
         <v>22</v>
       </c>
@@ -13928,7 +13925,7 @@
       <c r="K310" s="16"/>
       <c r="L310" s="16"/>
     </row>
-    <row r="311" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A311" s="1" t="s">
         <v>13</v>
       </c>
@@ -13954,7 +13951,7 @@
         <v>2.68</v>
       </c>
     </row>
-    <row r="312" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A312" s="1" t="s">
         <v>16</v>
       </c>
@@ -13980,7 +13977,7 @@
         <v>2.11</v>
       </c>
     </row>
-    <row r="313" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A313" s="1" t="s">
         <v>19</v>
       </c>
@@ -14006,7 +14003,7 @@
         <v>2.11</v>
       </c>
     </row>
-    <row r="314" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A314" s="29" t="s">
         <v>22</v>
       </c>
@@ -14030,7 +14027,7 @@
       <c r="K314" s="11"/>
       <c r="L314" s="11"/>
     </row>
-    <row r="315" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A315" s="1" t="s">
         <v>16</v>
       </c>
@@ -14056,7 +14053,7 @@
         <v>0.57999999999999996</v>
       </c>
     </row>
-    <row r="316" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A316" s="1" t="s">
         <v>19</v>
       </c>
@@ -14082,7 +14079,7 @@
         <v>0.57999999999999996</v>
       </c>
     </row>
-    <row r="317" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A317" s="29" t="s">
         <v>22</v>
       </c>
@@ -14106,7 +14103,7 @@
       <c r="K317" s="11"/>
       <c r="L317" s="11"/>
     </row>
-    <row r="318" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A318" s="29" t="s">
         <v>22</v>
       </c>
@@ -14130,7 +14127,7 @@
       <c r="K318" s="11"/>
       <c r="L318" s="11"/>
     </row>
-    <row r="319" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A319" s="1" t="s">
         <v>10</v>
       </c>
@@ -14156,7 +14153,7 @@
         <v>5.99</v>
       </c>
     </row>
-    <row r="320" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A320" s="1" t="s">
         <v>13</v>
       </c>
@@ -14182,7 +14179,7 @@
         <v>0.85</v>
       </c>
     </row>
-    <row r="321" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A321" s="1" t="s">
         <v>16</v>
       </c>
@@ -14208,7 +14205,7 @@
         <v>0.85</v>
       </c>
     </row>
-    <row r="322" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A322" s="1" t="s">
         <v>19</v>
       </c>
@@ -14234,7 +14231,7 @@
         <v>0.74</v>
       </c>
     </row>
-    <row r="323" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:12" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A323" s="7" t="s">
         <v>22</v>
       </c>
@@ -14258,7 +14255,7 @@
       <c r="K323" s="16"/>
       <c r="L323" s="16"/>
     </row>
-    <row r="324" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:12" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A324" s="7" t="s">
         <v>22</v>
       </c>
@@ -14282,7 +14279,7 @@
       <c r="K324" s="16"/>
       <c r="L324" s="16"/>
     </row>
-    <row r="325" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A325" s="7" t="s">
         <v>22</v>
       </c>
@@ -14306,7 +14303,7 @@
       <c r="K325" s="16"/>
       <c r="L325" s="16"/>
     </row>
-    <row r="326" spans="1:12" ht="63.75" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:12" ht="66" x14ac:dyDescent="0.3">
       <c r="A326" s="7" t="s">
         <v>22</v>
       </c>
@@ -14330,7 +14327,7 @@
       <c r="K326" s="16"/>
       <c r="L326" s="16"/>
     </row>
-    <row r="327" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:12" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A327" s="7" t="s">
         <v>22</v>
       </c>
@@ -14354,7 +14351,7 @@
       <c r="K327" s="16"/>
       <c r="L327" s="16"/>
     </row>
-    <row r="328" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A328" s="7" t="s">
         <v>22</v>
       </c>
@@ -14378,7 +14375,7 @@
       <c r="K328" s="16"/>
       <c r="L328" s="16"/>
     </row>
-    <row r="329" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A329" s="1" t="s">
         <v>19</v>
       </c>
@@ -14404,7 +14401,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="330" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A330" s="7" t="s">
         <v>22</v>
       </c>
@@ -14428,7 +14425,7 @@
       <c r="K330" s="16"/>
       <c r="L330" s="16"/>
     </row>
-    <row r="331" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A331" s="1" t="s">
         <v>19</v>
       </c>
@@ -14454,7 +14451,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="332" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A332" s="7" t="s">
         <v>22</v>
       </c>
@@ -14478,7 +14475,7 @@
       <c r="K332" s="16"/>
       <c r="L332" s="16"/>
     </row>
-    <row r="333" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A333" s="1" t="s">
         <v>13</v>
       </c>
@@ -14504,7 +14501,7 @@
         <v>0.23</v>
       </c>
     </row>
-    <row r="334" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A334" s="1" t="s">
         <v>16</v>
       </c>
@@ -14530,7 +14527,7 @@
         <v>0.23</v>
       </c>
     </row>
-    <row r="335" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A335" s="1" t="s">
         <v>19</v>
       </c>
@@ -14556,7 +14553,7 @@
         <v>0.18</v>
       </c>
     </row>
-    <row r="336" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A336" s="7" t="s">
         <v>22</v>
       </c>
@@ -14580,7 +14577,7 @@
       <c r="K336" s="16"/>
       <c r="L336" s="16"/>
     </row>
-    <row r="337" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:12" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A337" s="7" t="s">
         <v>22</v>
       </c>
@@ -14604,7 +14601,7 @@
       <c r="K337" s="16"/>
       <c r="L337" s="16"/>
     </row>
-    <row r="338" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A338" s="7" t="s">
         <v>22</v>
       </c>
@@ -14628,7 +14625,7 @@
       <c r="K338" s="16"/>
       <c r="L338" s="16"/>
     </row>
-    <row r="339" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A339" s="7" t="s">
         <v>22</v>
       </c>
@@ -14652,7 +14649,7 @@
       <c r="K339" s="16"/>
       <c r="L339" s="16"/>
     </row>
-    <row r="340" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A340" s="1" t="s">
         <v>19</v>
       </c>
@@ -14678,7 +14675,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="341" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A341" s="7" t="s">
         <v>22</v>
       </c>
@@ -14702,7 +14699,7 @@
       <c r="K341" s="16"/>
       <c r="L341" s="16"/>
     </row>
-    <row r="342" spans="1:12" ht="51" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:12" ht="52.8" x14ac:dyDescent="0.3">
       <c r="A342" s="7" t="s">
         <v>22</v>
       </c>
@@ -14726,7 +14723,7 @@
       <c r="K342" s="16"/>
       <c r="L342" s="16"/>
     </row>
-    <row r="343" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A343" s="1" t="s">
         <v>13</v>
       </c>
@@ -14752,7 +14749,7 @@
         <v>0.32</v>
       </c>
     </row>
-    <row r="344" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A344" s="1" t="s">
         <v>16</v>
       </c>
@@ -14778,7 +14775,7 @@
         <v>0.28999999999999998</v>
       </c>
     </row>
-    <row r="345" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A345" s="1" t="s">
         <v>19</v>
       </c>
@@ -14804,7 +14801,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="346" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A346" s="7" t="s">
         <v>22</v>
       </c>
@@ -14828,7 +14825,7 @@
       <c r="K346" s="16"/>
       <c r="L346" s="16"/>
     </row>
-    <row r="347" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A347" s="1" t="s">
         <v>19</v>
       </c>
@@ -14854,7 +14851,7 @@
         <v>0.13</v>
       </c>
     </row>
-    <row r="348" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A348" s="7" t="s">
         <v>22</v>
       </c>
@@ -14878,7 +14875,7 @@
       <c r="K348" s="16"/>
       <c r="L348" s="16"/>
     </row>
-    <row r="349" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A349" s="1" t="s">
         <v>19</v>
       </c>
@@ -14904,7 +14901,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="350" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A350" s="7" t="s">
         <v>22</v>
       </c>
@@ -14928,7 +14925,7 @@
       <c r="K350" s="16"/>
       <c r="L350" s="16"/>
     </row>
-    <row r="351" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A351" s="7" t="s">
         <v>22</v>
       </c>
@@ -14952,7 +14949,7 @@
       <c r="K351" s="16"/>
       <c r="L351" s="16"/>
     </row>
-    <row r="352" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:12" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A352" s="7" t="s">
         <v>22</v>
       </c>
@@ -14976,7 +14973,7 @@
       <c r="K352" s="16"/>
       <c r="L352" s="16"/>
     </row>
-    <row r="353" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A353" s="1" t="s">
         <v>16</v>
       </c>
@@ -15002,7 +14999,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="354" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A354" s="1" t="s">
         <v>19</v>
       </c>
@@ -15028,7 +15025,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="355" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A355" s="7" t="s">
         <v>22</v>
       </c>
@@ -15052,7 +15049,7 @@
       <c r="K355" s="16"/>
       <c r="L355" s="16"/>
     </row>
-    <row r="356" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:12" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A356" s="7" t="s">
         <v>22</v>
       </c>
@@ -15076,7 +15073,7 @@
       <c r="K356" s="16"/>
       <c r="L356" s="16"/>
     </row>
-    <row r="357" spans="1:12" ht="51" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:12" ht="52.8" x14ac:dyDescent="0.3">
       <c r="A357" s="7" t="s">
         <v>22</v>
       </c>
@@ -15100,7 +15097,7 @@
       <c r="K357" s="16"/>
       <c r="L357" s="16"/>
     </row>
-    <row r="358" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A358" s="1" t="s">
         <v>13</v>
       </c>
@@ -15126,7 +15123,7 @@
         <v>0.17</v>
       </c>
     </row>
-    <row r="359" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A359" s="1" t="s">
         <v>16</v>
       </c>
@@ -15152,7 +15149,7 @@
         <v>0.17</v>
       </c>
     </row>
-    <row r="360" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A360" s="1" t="s">
         <v>19</v>
       </c>
@@ -15178,7 +15175,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="361" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:12" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A361" s="7" t="s">
         <v>22</v>
       </c>
@@ -15202,7 +15199,7 @@
       <c r="K361" s="16"/>
       <c r="L361" s="16"/>
     </row>
-    <row r="362" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A362" s="1" t="s">
         <v>19</v>
       </c>
@@ -15228,7 +15225,7 @@
         <v>0.11</v>
       </c>
     </row>
-    <row r="363" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A363" s="7" t="s">
         <v>22</v>
       </c>
@@ -15252,7 +15249,7 @@
       <c r="K363" s="16"/>
       <c r="L363" s="16"/>
     </row>
-    <row r="364" spans="1:12" ht="51" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:12" ht="52.8" x14ac:dyDescent="0.3">
       <c r="A364" s="7" t="s">
         <v>22</v>
       </c>
@@ -15276,7 +15273,7 @@
       <c r="K364" s="16"/>
       <c r="L364" s="16"/>
     </row>
-    <row r="365" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:12" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A365" s="7" t="s">
         <v>22</v>
       </c>
@@ -15300,7 +15297,7 @@
       <c r="K365" s="16"/>
       <c r="L365" s="16"/>
     </row>
-    <row r="366" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A366" s="1" t="s">
         <v>13</v>
       </c>
@@ -15326,7 +15323,7 @@
         <v>0.13</v>
       </c>
     </row>
-    <row r="367" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A367" s="1" t="s">
         <v>16</v>
       </c>
@@ -15352,7 +15349,7 @@
         <v>0.13</v>
       </c>
     </row>
-    <row r="368" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A368" s="1" t="s">
         <v>19</v>
       </c>
@@ -15378,7 +15375,7 @@
         <v>0.13</v>
       </c>
     </row>
-    <row r="369" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:12" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A369" s="7" t="s">
         <v>22</v>
       </c>
@@ -15402,7 +15399,7 @@
       <c r="K369" s="16"/>
       <c r="L369" s="16"/>
     </row>
-    <row r="370" spans="1:12" ht="51" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:12" ht="52.8" x14ac:dyDescent="0.3">
       <c r="A370" s="7" t="s">
         <v>22</v>
       </c>
@@ -15426,7 +15423,7 @@
       <c r="K370" s="16"/>
       <c r="L370" s="16"/>
     </row>
-    <row r="371" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A371" s="1" t="s">
         <v>13</v>
       </c>
@@ -15452,7 +15449,7 @@
         <v>4.29</v>
       </c>
     </row>
-    <row r="372" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A372" s="1" t="s">
         <v>16</v>
       </c>
@@ -15478,7 +15475,7 @@
         <v>1.33</v>
       </c>
     </row>
-    <row r="373" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A373" s="1" t="s">
         <v>19</v>
       </c>
@@ -15504,7 +15501,7 @@
         <v>0.98</v>
       </c>
     </row>
-    <row r="374" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A374" s="7" t="s">
         <v>22</v>
       </c>
@@ -15528,7 +15525,7 @@
       <c r="K374" s="16"/>
       <c r="L374" s="16"/>
     </row>
-    <row r="375" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A375" s="7" t="s">
         <v>22</v>
       </c>
@@ -15552,7 +15549,7 @@
       <c r="K375" s="16"/>
       <c r="L375" s="16"/>
     </row>
-    <row r="376" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A376" s="7" t="s">
         <v>22</v>
       </c>
@@ -15576,7 +15573,7 @@
       <c r="K376" s="16"/>
       <c r="L376" s="16"/>
     </row>
-    <row r="377" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A377" s="7" t="s">
         <v>22</v>
       </c>
@@ -15600,7 +15597,7 @@
       <c r="K377" s="16"/>
       <c r="L377" s="16"/>
     </row>
-    <row r="378" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A378" s="7" t="s">
         <v>22</v>
       </c>
@@ -15624,7 +15621,7 @@
       <c r="K378" s="16"/>
       <c r="L378" s="16"/>
     </row>
-    <row r="379" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A379" s="7" t="s">
         <v>22</v>
       </c>
@@ -15648,7 +15645,7 @@
       <c r="K379" s="16"/>
       <c r="L379" s="16"/>
     </row>
-    <row r="380" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A380" s="7" t="s">
         <v>22</v>
       </c>
@@ -15672,7 +15669,7 @@
       <c r="K380" s="16"/>
       <c r="L380" s="16"/>
     </row>
-    <row r="381" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A381" s="1" t="s">
         <v>19</v>
       </c>
@@ -15698,7 +15695,7 @@
         <v>0.13</v>
       </c>
     </row>
-    <row r="382" spans="1:12" ht="51" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:12" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A382" s="7" t="s">
         <v>22</v>
       </c>
@@ -15722,7 +15719,7 @@
       <c r="K382" s="16"/>
       <c r="L382" s="16"/>
     </row>
-    <row r="383" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A383" s="7" t="s">
         <v>22</v>
       </c>
@@ -15746,7 +15743,7 @@
       <c r="K383" s="16"/>
       <c r="L383" s="16"/>
     </row>
-    <row r="384" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A384" s="7" t="s">
         <v>22</v>
       </c>
@@ -15770,7 +15767,7 @@
       <c r="K384" s="16"/>
       <c r="L384" s="16"/>
     </row>
-    <row r="385" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A385" s="1" t="s">
         <v>19</v>
       </c>
@@ -15796,7 +15793,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="386" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:12" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A386" s="7" t="s">
         <v>22</v>
       </c>
@@ -15820,7 +15817,7 @@
       <c r="K386" s="16"/>
       <c r="L386" s="16"/>
     </row>
-    <row r="387" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A387" s="1" t="s">
         <v>19</v>
       </c>
@@ -15846,7 +15843,7 @@
         <v>0.19</v>
       </c>
     </row>
-    <row r="388" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A388" s="7" t="s">
         <v>22</v>
       </c>
@@ -15870,7 +15867,7 @@
       <c r="K388" s="16"/>
       <c r="L388" s="16"/>
     </row>
-    <row r="389" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A389" s="7" t="s">
         <v>22</v>
       </c>
@@ -15894,7 +15891,7 @@
       <c r="K389" s="16"/>
       <c r="L389" s="16"/>
     </row>
-    <row r="390" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:12" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A390" s="7" t="s">
         <v>22</v>
       </c>
@@ -15918,7 +15915,7 @@
       <c r="K390" s="16"/>
       <c r="L390" s="16"/>
     </row>
-    <row r="391" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A391" s="7" t="s">
         <v>22</v>
       </c>
@@ -15942,7 +15939,7 @@
       <c r="K391" s="16"/>
       <c r="L391" s="16"/>
     </row>
-    <row r="392" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:12" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A392" s="7" t="s">
         <v>22</v>
       </c>
@@ -15966,7 +15963,7 @@
       <c r="K392" s="16"/>
       <c r="L392" s="16"/>
     </row>
-    <row r="393" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A393" s="7" t="s">
         <v>22</v>
       </c>
@@ -15990,7 +15987,7 @@
       <c r="K393" s="16"/>
       <c r="L393" s="16"/>
     </row>
-    <row r="394" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A394" s="1" t="s">
         <v>16</v>
       </c>
@@ -16016,7 +16013,7 @@
         <v>2.95</v>
       </c>
     </row>
-    <row r="395" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A395" s="1" t="s">
         <v>19</v>
       </c>
@@ -16042,7 +16039,7 @@
         <v>2.95</v>
       </c>
     </row>
-    <row r="396" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A396" s="7" t="s">
         <v>22</v>
       </c>
@@ -16066,7 +16063,7 @@
       <c r="K396" s="16"/>
       <c r="L396" s="16"/>
     </row>
-    <row r="397" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A397" s="1" t="s">
         <v>10</v>
       </c>
@@ -16092,7 +16089,7 @@
         <v>2.34</v>
       </c>
     </row>
-    <row r="398" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A398" s="1" t="s">
         <v>13</v>
       </c>
@@ -16118,7 +16115,7 @@
         <v>1.46</v>
       </c>
     </row>
-    <row r="399" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A399" s="1" t="s">
         <v>16</v>
       </c>
@@ -16144,7 +16141,7 @@
         <v>1.29</v>
       </c>
     </row>
-    <row r="400" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A400" s="1" t="s">
         <v>19</v>
       </c>
@@ -16170,7 +16167,7 @@
         <v>1.29</v>
       </c>
     </row>
-    <row r="401" spans="1:12" ht="76.5" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:12" ht="79.2" x14ac:dyDescent="0.3">
       <c r="A401" s="7" t="s">
         <v>22</v>
       </c>
@@ -16194,7 +16191,7 @@
       <c r="K401" s="16"/>
       <c r="L401" s="16"/>
     </row>
-    <row r="402" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A402" s="7" t="s">
         <v>22</v>
       </c>
@@ -16218,7 +16215,7 @@
       <c r="K402" s="16"/>
       <c r="L402" s="16"/>
     </row>
-    <row r="403" spans="1:12" ht="102" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:12" ht="105.6" x14ac:dyDescent="0.3">
       <c r="A403" s="7" t="s">
         <v>22</v>
       </c>
@@ -16242,7 +16239,7 @@
       <c r="K403" s="16"/>
       <c r="L403" s="16"/>
     </row>
-    <row r="404" spans="1:12" ht="51" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:12" ht="52.8" x14ac:dyDescent="0.3">
       <c r="A404" s="7" t="s">
         <v>22</v>
       </c>
@@ -16266,7 +16263,7 @@
       <c r="K404" s="16"/>
       <c r="L404" s="16"/>
     </row>
-    <row r="405" spans="1:12" ht="76.5" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:12" ht="79.2" x14ac:dyDescent="0.3">
       <c r="A405" s="7" t="s">
         <v>22</v>
       </c>
@@ -16290,7 +16287,7 @@
       <c r="K405" s="16"/>
       <c r="L405" s="16"/>
     </row>
-    <row r="406" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A406" s="7" t="s">
         <v>22</v>
       </c>
@@ -16314,7 +16311,7 @@
       <c r="K406" s="16"/>
       <c r="L406" s="16"/>
     </row>
-    <row r="407" spans="1:12" ht="63.75" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:12" ht="66" x14ac:dyDescent="0.3">
       <c r="A407" s="7" t="s">
         <v>22</v>
       </c>
@@ -16338,7 +16335,7 @@
       <c r="K407" s="16"/>
       <c r="L407" s="16"/>
     </row>
-    <row r="408" spans="1:12" ht="63.75" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:12" ht="66" x14ac:dyDescent="0.3">
       <c r="A408" s="7" t="s">
         <v>22</v>
       </c>
@@ -16362,7 +16359,7 @@
       <c r="K408" s="16"/>
       <c r="L408" s="16"/>
     </row>
-    <row r="409" spans="1:12" ht="51" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:12" ht="52.8" x14ac:dyDescent="0.3">
       <c r="A409" s="7" t="s">
         <v>22</v>
       </c>
@@ -16386,7 +16383,7 @@
       <c r="K409" s="16"/>
       <c r="L409" s="16"/>
     </row>
-    <row r="410" spans="1:12" ht="63.75" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:12" ht="66" x14ac:dyDescent="0.3">
       <c r="A410" s="7" t="s">
         <v>22</v>
       </c>
@@ -16410,7 +16407,7 @@
       <c r="K410" s="16"/>
       <c r="L410" s="16"/>
     </row>
-    <row r="411" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A411" s="7" t="s">
         <v>22</v>
       </c>
@@ -16434,7 +16431,7 @@
       <c r="K411" s="16"/>
       <c r="L411" s="16"/>
     </row>
-    <row r="412" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A412" s="1" t="s">
         <v>16</v>
       </c>
@@ -16460,7 +16457,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="413" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A413" s="1" t="s">
         <v>19</v>
       </c>
@@ -16486,7 +16483,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="414" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A414" s="7" t="s">
         <v>22</v>
       </c>
@@ -16510,7 +16507,7 @@
       <c r="K414" s="16"/>
       <c r="L414" s="16"/>
     </row>
-    <row r="415" spans="1:12" ht="114.75" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:12" ht="118.8" x14ac:dyDescent="0.3">
       <c r="A415" s="7" t="s">
         <v>22</v>
       </c>
@@ -16534,7 +16531,7 @@
       <c r="K415" s="16"/>
       <c r="L415" s="16"/>
     </row>
-    <row r="416" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A416" s="7" t="s">
         <v>22</v>
       </c>
@@ -16558,7 +16555,7 @@
       <c r="K416" s="16"/>
       <c r="L416" s="16"/>
     </row>
-    <row r="417" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A417" s="1" t="s">
         <v>16</v>
       </c>
@@ -16584,7 +16581,7 @@
         <v>0.14000000000000001</v>
       </c>
     </row>
-    <row r="418" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A418" s="1" t="s">
         <v>19</v>
       </c>
@@ -16610,7 +16607,7 @@
         <v>0.14000000000000001</v>
       </c>
     </row>
-    <row r="419" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A419" s="7" t="s">
         <v>22</v>
       </c>
@@ -16634,7 +16631,7 @@
       <c r="K419" s="16"/>
       <c r="L419" s="16"/>
     </row>
-    <row r="420" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A420" s="1" t="s">
         <v>13</v>
       </c>
@@ -16660,7 +16657,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="421" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A421" s="1" t="s">
         <v>16</v>
       </c>
@@ -16686,7 +16683,7 @@
         <v>0.27</v>
       </c>
     </row>
-    <row r="422" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A422" s="1" t="s">
         <v>19</v>
       </c>
@@ -16712,7 +16709,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="423" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A423" s="7" t="s">
         <v>22</v>
       </c>
@@ -16736,7 +16733,7 @@
       <c r="K423" s="16"/>
       <c r="L423" s="16"/>
     </row>
-    <row r="424" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A424" s="1" t="s">
         <v>19</v>
       </c>
@@ -16762,7 +16759,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="425" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:12" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A425" s="7" t="s">
         <v>22</v>
       </c>
@@ -16786,7 +16783,7 @@
       <c r="K425" s="16"/>
       <c r="L425" s="16"/>
     </row>
-    <row r="426" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:12" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A426" s="7" t="s">
         <v>22</v>
       </c>
@@ -16810,7 +16807,7 @@
       <c r="K426" s="16"/>
       <c r="L426" s="16"/>
     </row>
-    <row r="427" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A427" s="7" t="s">
         <v>22</v>
       </c>
@@ -16834,7 +16831,7 @@
       <c r="K427" s="16"/>
       <c r="L427" s="16"/>
     </row>
-    <row r="428" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A428" s="1" t="s">
         <v>16</v>
       </c>
@@ -16860,7 +16857,7 @@
         <v>0.39</v>
       </c>
     </row>
-    <row r="429" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A429" s="1" t="s">
         <v>19</v>
       </c>
@@ -16886,7 +16883,7 @@
         <v>0.39</v>
       </c>
     </row>
-    <row r="430" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A430" s="7" t="s">
         <v>22</v>
       </c>
@@ -16910,7 +16907,7 @@
       <c r="K430" s="16"/>
       <c r="L430" s="16"/>
     </row>
-    <row r="431" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A431" s="1" t="s">
         <v>16</v>
       </c>
@@ -16936,7 +16933,7 @@
         <v>0.13</v>
       </c>
     </row>
-    <row r="432" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A432" s="1" t="s">
         <v>19</v>
       </c>
@@ -16962,7 +16959,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="433" spans="1:12" ht="127.5" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:12" ht="132" x14ac:dyDescent="0.3">
       <c r="A433" s="7" t="s">
         <v>22</v>
       </c>
@@ -16986,7 +16983,7 @@
       <c r="K433" s="16"/>
       <c r="L433" s="16"/>
     </row>
-    <row r="434" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:12" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A434" s="7" t="s">
         <v>22</v>
       </c>
@@ -17010,7 +17007,7 @@
       <c r="K434" s="16"/>
       <c r="L434" s="16"/>
     </row>
-    <row r="435" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A435" s="1" t="s">
         <v>19</v>
       </c>
@@ -17036,7 +17033,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="436" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A436" s="7" t="s">
         <v>22</v>
       </c>
@@ -17060,7 +17057,7 @@
       <c r="K436" s="16"/>
       <c r="L436" s="16"/>
     </row>
-    <row r="437" spans="1:12" ht="140.25" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:12" ht="145.19999999999999" x14ac:dyDescent="0.3">
       <c r="A437" s="7" t="s">
         <v>22</v>
       </c>
@@ -17084,7 +17081,7 @@
       <c r="K437" s="16"/>
       <c r="L437" s="16"/>
     </row>
-    <row r="438" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A438" s="1" t="s">
         <v>19</v>
       </c>
@@ -17110,7 +17107,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="439" spans="1:12" ht="63.75" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:12" ht="66" x14ac:dyDescent="0.3">
       <c r="A439" s="7" t="s">
         <v>22</v>
       </c>
@@ -17134,7 +17131,7 @@
       <c r="K439" s="16"/>
       <c r="L439" s="16"/>
     </row>
-    <row r="440" spans="1:12" ht="51" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:12" ht="52.8" x14ac:dyDescent="0.3">
       <c r="A440" s="7" t="s">
         <v>22</v>
       </c>
@@ -17158,7 +17155,7 @@
       <c r="K440" s="16"/>
       <c r="L440" s="16"/>
     </row>
-    <row r="441" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A441" s="1" t="s">
         <v>13</v>
       </c>
@@ -17184,7 +17181,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="442" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A442" s="1" t="s">
         <v>16</v>
       </c>
@@ -17210,7 +17207,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="443" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A443" s="1" t="s">
         <v>19</v>
       </c>
@@ -17236,7 +17233,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="444" spans="1:12" ht="63.75" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:12" ht="66" x14ac:dyDescent="0.3">
       <c r="A444" s="7" t="s">
         <v>22</v>
       </c>
@@ -17260,7 +17257,7 @@
       <c r="K444" s="16"/>
       <c r="L444" s="16"/>
     </row>
-    <row r="445" spans="1:12" ht="63.75" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:12" ht="66" x14ac:dyDescent="0.3">
       <c r="A445" s="7" t="s">
         <v>22</v>
       </c>
@@ -17284,7 +17281,7 @@
       <c r="K445" s="16"/>
       <c r="L445" s="16"/>
     </row>
-    <row r="446" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A446" s="1" t="s">
         <v>10</v>
       </c>
@@ -17310,7 +17307,7 @@
         <v>15.12</v>
       </c>
     </row>
-    <row r="447" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A447" s="1" t="s">
         <v>13</v>
       </c>
@@ -17336,7 +17333,7 @@
         <v>5.41</v>
       </c>
     </row>
-    <row r="448" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A448" s="1" t="s">
         <v>16</v>
       </c>
@@ -17362,7 +17359,7 @@
         <v>5.21</v>
       </c>
     </row>
-    <row r="449" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A449" s="1" t="s">
         <v>19</v>
       </c>
@@ -17388,7 +17385,7 @@
         <v>5.21</v>
       </c>
     </row>
-    <row r="450" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A450" s="7" t="s">
         <v>22</v>
       </c>
@@ -17412,7 +17409,7 @@
       <c r="K450" s="16"/>
       <c r="L450" s="16"/>
     </row>
-    <row r="451" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A451" s="7" t="s">
         <v>22</v>
       </c>
@@ -17436,7 +17433,7 @@
       <c r="K451" s="16"/>
       <c r="L451" s="16"/>
     </row>
-    <row r="452" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A452" s="1" t="s">
         <v>16</v>
       </c>
@@ -17462,7 +17459,7 @@
         <v>0.13</v>
       </c>
     </row>
-    <row r="453" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A453" s="1" t="s">
         <v>19</v>
       </c>
@@ -17488,7 +17485,7 @@
         <v>0.13</v>
       </c>
     </row>
-    <row r="454" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:12" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A454" s="7" t="s">
         <v>22</v>
       </c>
@@ -17512,7 +17509,7 @@
       <c r="K454" s="16"/>
       <c r="L454" s="16"/>
     </row>
-    <row r="455" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A455" s="1" t="s">
         <v>16</v>
       </c>
@@ -17538,7 +17535,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="456" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A456" s="1" t="s">
         <v>19</v>
       </c>
@@ -17564,7 +17561,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="457" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A457" s="7" t="s">
         <v>22</v>
       </c>
@@ -17588,7 +17585,7 @@
       <c r="K457" s="16"/>
       <c r="L457" s="16"/>
     </row>
-    <row r="458" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A458" s="1" t="s">
         <v>13</v>
       </c>
@@ -17614,7 +17611,7 @@
         <v>5.84</v>
       </c>
     </row>
-    <row r="459" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A459" s="1" t="s">
         <v>16</v>
       </c>
@@ -17640,7 +17637,7 @@
         <v>0.39</v>
       </c>
     </row>
-    <row r="460" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A460" s="1" t="s">
         <v>19</v>
       </c>
@@ -17666,7 +17663,7 @@
         <v>0.11</v>
       </c>
     </row>
-    <row r="461" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A461" s="7" t="s">
         <v>22</v>
       </c>
@@ -17690,7 +17687,7 @@
       <c r="K461" s="16"/>
       <c r="L461" s="16"/>
     </row>
-    <row r="462" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A462" s="1" t="s">
         <v>19</v>
       </c>
@@ -17716,7 +17713,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="463" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A463" s="7" t="s">
         <v>22</v>
       </c>
@@ -17740,7 +17737,7 @@
       <c r="K463" s="16"/>
       <c r="L463" s="16"/>
     </row>
-    <row r="464" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A464" s="1" t="s">
         <v>19</v>
       </c>
@@ -17766,7 +17763,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="465" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A465" s="7" t="s">
         <v>22</v>
       </c>
@@ -17790,7 +17787,7 @@
       <c r="K465" s="16"/>
       <c r="L465" s="16"/>
     </row>
-    <row r="466" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A466" s="7" t="s">
         <v>22</v>
       </c>
@@ -17814,7 +17811,7 @@
       <c r="K466" s="16"/>
       <c r="L466" s="16"/>
     </row>
-    <row r="467" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A467" s="1" t="s">
         <v>19</v>
       </c>
@@ -17840,7 +17837,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="468" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A468" s="7" t="s">
         <v>22</v>
       </c>
@@ -17864,7 +17861,7 @@
       <c r="K468" s="16"/>
       <c r="L468" s="16"/>
     </row>
-    <row r="469" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A469" s="1" t="s">
         <v>16</v>
       </c>
@@ -17890,7 +17887,7 @@
         <v>3.44</v>
       </c>
     </row>
-    <row r="470" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A470" s="1" t="s">
         <v>19</v>
       </c>
@@ -17916,7 +17913,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="471" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A471" s="7" t="s">
         <v>22</v>
       </c>
@@ -17940,7 +17937,7 @@
       <c r="K471" s="16"/>
       <c r="L471" s="16"/>
     </row>
-    <row r="472" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A472" s="1" t="s">
         <v>19</v>
       </c>
@@ -17966,7 +17963,7 @@
         <v>3.39</v>
       </c>
     </row>
-    <row r="473" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A473" s="7" t="s">
         <v>22</v>
       </c>
@@ -17990,7 +17987,7 @@
       <c r="K473" s="16"/>
       <c r="L473" s="16"/>
     </row>
-    <row r="474" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A474" s="7" t="s">
         <v>22</v>
       </c>
@@ -18014,7 +18011,7 @@
       <c r="K474" s="16"/>
       <c r="L474" s="16"/>
     </row>
-    <row r="475" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A475" s="7" t="s">
         <v>22</v>
       </c>
@@ -18038,7 +18035,7 @@
       <c r="K475" s="16"/>
       <c r="L475" s="16"/>
     </row>
-    <row r="476" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A476" s="7" t="s">
         <v>22</v>
       </c>
@@ -18062,7 +18059,7 @@
       <c r="K476" s="16"/>
       <c r="L476" s="16"/>
     </row>
-    <row r="477" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A477" s="1" t="s">
         <v>16</v>
       </c>
@@ -18088,7 +18085,7 @@
         <v>1.02</v>
       </c>
     </row>
-    <row r="478" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A478" s="1" t="s">
         <v>19</v>
       </c>
@@ -18114,7 +18111,7 @@
         <v>0.73</v>
       </c>
     </row>
-    <row r="479" spans="1:12" ht="165.75" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:12" ht="171.6" x14ac:dyDescent="0.3">
       <c r="A479" s="7" t="s">
         <v>22</v>
       </c>
@@ -18138,7 +18135,7 @@
       <c r="K479" s="16"/>
       <c r="L479" s="16"/>
     </row>
-    <row r="480" spans="1:12" ht="89.25" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:12" ht="92.4" x14ac:dyDescent="0.3">
       <c r="A480" s="7" t="s">
         <v>22</v>
       </c>
@@ -18162,7 +18159,7 @@
       <c r="K480" s="16"/>
       <c r="L480" s="16"/>
     </row>
-    <row r="481" spans="1:12" ht="63.75" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:12" ht="66" x14ac:dyDescent="0.3">
       <c r="A481" s="7" t="s">
         <v>22</v>
       </c>
@@ -18186,7 +18183,7 @@
       <c r="K481" s="16"/>
       <c r="L481" s="16"/>
     </row>
-    <row r="482" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A482" s="1" t="s">
         <v>19</v>
       </c>
@@ -18212,7 +18209,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="483" spans="1:12" ht="51" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:12" ht="52.8" x14ac:dyDescent="0.3">
       <c r="A483" s="7" t="s">
         <v>22</v>
       </c>
@@ -18236,7 +18233,7 @@
       <c r="K483" s="16"/>
       <c r="L483" s="16"/>
     </row>
-    <row r="484" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A484" s="1" t="s">
         <v>19</v>
       </c>
@@ -18262,7 +18259,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="485" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:12" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A485" s="7" t="s">
         <v>22</v>
       </c>
@@ -18286,7 +18283,7 @@
       <c r="K485" s="16"/>
       <c r="L485" s="16"/>
     </row>
-    <row r="486" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A486" s="1" t="s">
         <v>16</v>
       </c>
@@ -18312,7 +18309,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="487" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A487" s="1" t="s">
         <v>19</v>
       </c>
@@ -18338,7 +18335,7 @@
         <v>0.53</v>
       </c>
     </row>
-    <row r="488" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A488" s="7" t="s">
         <v>22</v>
       </c>
@@ -18362,7 +18359,7 @@
       <c r="K488" s="16"/>
       <c r="L488" s="16"/>
     </row>
-    <row r="489" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A489" s="7" t="s">
         <v>22</v>
       </c>
@@ -18386,7 +18383,7 @@
       <c r="K489" s="16"/>
       <c r="L489" s="16"/>
     </row>
-    <row r="490" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A490" s="1" t="s">
         <v>19</v>
       </c>
@@ -18412,7 +18409,7 @@
         <v>0.36</v>
       </c>
     </row>
-    <row r="491" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A491" s="7" t="s">
         <v>22</v>
       </c>
@@ -18436,7 +18433,7 @@
       <c r="K491" s="16"/>
       <c r="L491" s="16"/>
     </row>
-    <row r="492" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A492" s="1" t="s">
         <v>19</v>
       </c>
@@ -18462,7 +18459,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="493" spans="1:12" ht="63.75" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:12" ht="66" x14ac:dyDescent="0.3">
       <c r="A493" s="7" t="s">
         <v>22</v>
       </c>
@@ -18486,7 +18483,7 @@
       <c r="K493" s="16"/>
       <c r="L493" s="16"/>
     </row>
-    <row r="494" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A494" s="1" t="s">
         <v>13</v>
       </c>
@@ -18512,7 +18509,7 @@
         <v>3.86</v>
       </c>
     </row>
-    <row r="495" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A495" s="1" t="s">
         <v>16</v>
       </c>
@@ -18538,7 +18535,7 @@
         <v>0.69</v>
       </c>
     </row>
-    <row r="496" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A496" s="1" t="s">
         <v>19</v>
       </c>
@@ -18564,7 +18561,7 @@
         <v>0.69</v>
       </c>
     </row>
-    <row r="497" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A497" s="7" t="s">
         <v>22</v>
       </c>
@@ -18588,7 +18585,7 @@
       <c r="K497" s="16"/>
       <c r="L497" s="16"/>
     </row>
-    <row r="498" spans="1:12" ht="51" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:12" ht="52.8" x14ac:dyDescent="0.3">
       <c r="A498" s="7" t="s">
         <v>22</v>
       </c>
@@ -18612,7 +18609,7 @@
       <c r="K498" s="16"/>
       <c r="L498" s="16"/>
     </row>
-    <row r="499" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A499" s="1" t="s">
         <v>16</v>
       </c>
@@ -18638,7 +18635,7 @@
         <v>3.17</v>
       </c>
     </row>
-    <row r="500" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A500" s="1" t="s">
         <v>19</v>
       </c>
@@ -18664,7 +18661,7 @@
         <v>2.4700000000000002</v>
       </c>
     </row>
-    <row r="501" spans="1:12" ht="76.5" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:12" ht="79.2" x14ac:dyDescent="0.3">
       <c r="A501" s="7" t="s">
         <v>22</v>
       </c>
@@ -18688,7 +18685,7 @@
       <c r="K501" s="16"/>
       <c r="L501" s="16"/>
     </row>
-    <row r="502" spans="1:12" ht="76.5" x14ac:dyDescent="0.25">
+    <row r="502" spans="1:12" ht="79.2" x14ac:dyDescent="0.3">
       <c r="A502" s="7" t="s">
         <v>22</v>
       </c>
@@ -18712,7 +18709,7 @@
       <c r="K502" s="16"/>
       <c r="L502" s="16"/>
     </row>
-    <row r="503" spans="1:12" ht="63.75" x14ac:dyDescent="0.25">
+    <row r="503" spans="1:12" ht="66" x14ac:dyDescent="0.3">
       <c r="A503" s="7" t="s">
         <v>22</v>
       </c>
@@ -18736,7 +18733,7 @@
       <c r="K503" s="16"/>
       <c r="L503" s="16"/>
     </row>
-    <row r="504" spans="1:12" ht="63.75" x14ac:dyDescent="0.25">
+    <row r="504" spans="1:12" ht="66" x14ac:dyDescent="0.3">
       <c r="A504" s="7" t="s">
         <v>22</v>
       </c>
@@ -18760,7 +18757,7 @@
       <c r="K504" s="16"/>
       <c r="L504" s="16"/>
     </row>
-    <row r="505" spans="1:12" ht="63.75" x14ac:dyDescent="0.25">
+    <row r="505" spans="1:12" ht="66" x14ac:dyDescent="0.3">
       <c r="A505" s="7" t="s">
         <v>22</v>
       </c>
@@ -18784,7 +18781,7 @@
       <c r="K505" s="16"/>
       <c r="L505" s="16"/>
     </row>
-    <row r="506" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="506" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A506" s="1" t="s">
         <v>19</v>
       </c>
@@ -18810,7 +18807,7 @@
         <v>0.23</v>
       </c>
     </row>
-    <row r="507" spans="1:12" ht="76.5" x14ac:dyDescent="0.25">
+    <row r="507" spans="1:12" ht="79.2" x14ac:dyDescent="0.3">
       <c r="A507" s="7" t="s">
         <v>22</v>
       </c>
@@ -18834,7 +18831,7 @@
       <c r="K507" s="16"/>
       <c r="L507" s="16"/>
     </row>
-    <row r="508" spans="1:12" ht="102" x14ac:dyDescent="0.25">
+    <row r="508" spans="1:12" ht="105.6" x14ac:dyDescent="0.3">
       <c r="A508" s="7" t="s">
         <v>22</v>
       </c>
@@ -18858,7 +18855,7 @@
       <c r="K508" s="16"/>
       <c r="L508" s="16"/>
     </row>
-    <row r="509" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="509" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A509" s="1" t="s">
         <v>19</v>
       </c>
@@ -18884,7 +18881,7 @@
         <v>0.48</v>
       </c>
     </row>
-    <row r="510" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="510" spans="1:12" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A510" s="7" t="s">
         <v>22</v>
       </c>
@@ -18908,7 +18905,7 @@
       <c r="K510" s="16"/>
       <c r="L510" s="16"/>
     </row>
-    <row r="511" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="511" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A511" s="1" t="s">
         <v>10</v>
       </c>
@@ -18934,7 +18931,7 @@
         <v>4.5599999999999996</v>
       </c>
     </row>
-    <row r="512" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="512" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A512" s="1" t="s">
         <v>13</v>
       </c>
@@ -18960,7 +18957,7 @@
         <v>0.46</v>
       </c>
     </row>
-    <row r="513" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="513" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A513" s="1" t="s">
         <v>16</v>
       </c>
@@ -18986,7 +18983,7 @@
         <v>0.46</v>
       </c>
     </row>
-    <row r="514" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="514" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A514" s="1" t="s">
         <v>19</v>
       </c>
@@ -19012,7 +19009,7 @@
         <v>0.46</v>
       </c>
     </row>
-    <row r="515" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="515" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A515" s="7" t="s">
         <v>22</v>
       </c>
@@ -19036,7 +19033,7 @@
       <c r="K515" s="16"/>
       <c r="L515" s="16"/>
     </row>
-    <row r="516" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="516" spans="1:12" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A516" s="7" t="s">
         <v>22</v>
       </c>
@@ -19060,7 +19057,7 @@
       <c r="K516" s="16"/>
       <c r="L516" s="16"/>
     </row>
-    <row r="517" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="517" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A517" s="1" t="s">
         <v>13</v>
       </c>
@@ -19086,7 +19083,7 @@
         <v>4.0999999999999996</v>
       </c>
     </row>
-    <row r="518" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="518" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A518" s="1" t="s">
         <v>16</v>
       </c>
@@ -19112,7 +19109,7 @@
         <v>4.0999999999999996</v>
       </c>
     </row>
-    <row r="519" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="519" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A519" s="1" t="s">
         <v>19</v>
       </c>
@@ -19138,7 +19135,7 @@
         <v>4.0999999999999996</v>
       </c>
     </row>
-    <row r="520" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="520" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A520" s="7" t="s">
         <v>22</v>
       </c>
@@ -19162,7 +19159,7 @@
       <c r="K520" s="16"/>
       <c r="L520" s="16"/>
     </row>
-    <row r="521" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="521" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A521" s="7" t="s">
         <v>22</v>
       </c>
@@ -19186,7 +19183,7 @@
       <c r="K521" s="16"/>
       <c r="L521" s="16"/>
     </row>
-    <row r="522" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="522" spans="1:12" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A522" s="7" t="s">
         <v>22</v>
       </c>
@@ -19210,7 +19207,7 @@
       <c r="K522" s="16"/>
       <c r="L522" s="16"/>
     </row>
-    <row r="523" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="523" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A523" s="7" t="s">
         <v>22</v>
       </c>
@@ -19234,7 +19231,7 @@
       <c r="K523" s="16"/>
       <c r="L523" s="16"/>
     </row>
-    <row r="524" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="524" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A524" s="7" t="s">
         <v>22</v>
       </c>
@@ -19258,7 +19255,7 @@
       <c r="K524" s="16"/>
       <c r="L524" s="16"/>
     </row>
-    <row r="525" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="525" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A525" s="1" t="s">
         <v>10</v>
       </c>
@@ -19284,7 +19281,7 @@
         <v>5.19</v>
       </c>
     </row>
-    <row r="526" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="526" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A526" s="1" t="s">
         <v>13</v>
       </c>
@@ -19310,7 +19307,7 @@
         <v>0.53</v>
       </c>
     </row>
-    <row r="527" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="527" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A527" s="1" t="s">
         <v>16</v>
       </c>
@@ -19336,7 +19333,7 @@
         <v>0.32</v>
       </c>
     </row>
-    <row r="528" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="528" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A528" s="1" t="s">
         <v>19</v>
       </c>
@@ -19362,7 +19359,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="529" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="529" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A529" s="7" t="s">
         <v>22</v>
       </c>
@@ -19386,7 +19383,7 @@
       <c r="K529" s="16"/>
       <c r="L529" s="16"/>
     </row>
-    <row r="530" spans="1:12" ht="51" x14ac:dyDescent="0.25">
+    <row r="530" spans="1:12" ht="52.8" x14ac:dyDescent="0.3">
       <c r="A530" s="7" t="s">
         <v>22</v>
       </c>
@@ -19410,7 +19407,7 @@
       <c r="K530" s="16"/>
       <c r="L530" s="16"/>
     </row>
-    <row r="531" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="531" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A531" s="7" t="s">
         <v>22</v>
       </c>
@@ -19434,7 +19431,7 @@
       <c r="K531" s="16"/>
       <c r="L531" s="16"/>
     </row>
-    <row r="532" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="532" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A532" s="1" t="s">
         <v>19</v>
       </c>
@@ -19460,7 +19457,7 @@
         <v>0.26</v>
       </c>
     </row>
-    <row r="533" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="533" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A533" s="7" t="s">
         <v>22</v>
       </c>
@@ -19484,7 +19481,7 @@
       <c r="K533" s="16"/>
       <c r="L533" s="16"/>
     </row>
-    <row r="534" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="534" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A534" s="1" t="s">
         <v>16</v>
       </c>
@@ -19510,7 +19507,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="535" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="535" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A535" s="1" t="s">
         <v>19</v>
       </c>
@@ -19536,7 +19533,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="536" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="536" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A536" s="7" t="s">
         <v>22</v>
       </c>
@@ -19560,7 +19557,7 @@
       <c r="K536" s="16"/>
       <c r="L536" s="16"/>
     </row>
-    <row r="537" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="537" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A537" s="7" t="s">
         <v>22</v>
       </c>
@@ -19584,7 +19581,7 @@
       <c r="K537" s="16"/>
       <c r="L537" s="16"/>
     </row>
-    <row r="538" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="538" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A538" s="1" t="s">
         <v>13</v>
       </c>
@@ -19610,7 +19607,7 @@
         <v>0.88</v>
       </c>
     </row>
-    <row r="539" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="539" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A539" s="1" t="s">
         <v>16</v>
       </c>
@@ -19636,7 +19633,7 @@
         <v>0.32</v>
       </c>
     </row>
-    <row r="540" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="540" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A540" s="1" t="s">
         <v>19</v>
       </c>
@@ -19662,7 +19659,7 @@
         <v>0.14000000000000001</v>
       </c>
     </row>
-    <row r="541" spans="1:12" ht="63.75" x14ac:dyDescent="0.25">
+    <row r="541" spans="1:12" ht="66" x14ac:dyDescent="0.3">
       <c r="A541" s="7" t="s">
         <v>22</v>
       </c>
@@ -19686,7 +19683,7 @@
       <c r="K541" s="16"/>
       <c r="L541" s="16"/>
     </row>
-    <row r="542" spans="1:12" ht="51" x14ac:dyDescent="0.25">
+    <row r="542" spans="1:12" ht="52.8" x14ac:dyDescent="0.3">
       <c r="A542" s="7" t="s">
         <v>22</v>
       </c>
@@ -19710,7 +19707,7 @@
       <c r="K542" s="16"/>
       <c r="L542" s="16"/>
     </row>
-    <row r="543" spans="1:12" ht="63.75" x14ac:dyDescent="0.25">
+    <row r="543" spans="1:12" ht="66" x14ac:dyDescent="0.3">
       <c r="A543" s="7" t="s">
         <v>22</v>
       </c>
@@ -19734,7 +19731,7 @@
       <c r="K543" s="16"/>
       <c r="L543" s="16"/>
     </row>
-    <row r="544" spans="1:12" ht="114.75" x14ac:dyDescent="0.25">
+    <row r="544" spans="1:12" ht="118.8" x14ac:dyDescent="0.3">
       <c r="A544" s="7" t="s">
         <v>22</v>
       </c>
@@ -19758,7 +19755,7 @@
       <c r="K544" s="16"/>
       <c r="L544" s="16"/>
     </row>
-    <row r="545" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="545" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A545" s="1" t="s">
         <v>19</v>
       </c>
@@ -19784,7 +19781,7 @@
         <v>0.18</v>
       </c>
     </row>
-    <row r="546" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="546" spans="1:12" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A546" s="7" t="s">
         <v>22</v>
       </c>
@@ -19808,7 +19805,7 @@
       <c r="K546" s="16"/>
       <c r="L546" s="16"/>
     </row>
-    <row r="547" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="547" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A547" s="7" t="s">
         <v>22</v>
       </c>
@@ -19832,7 +19829,7 @@
       <c r="K547" s="16"/>
       <c r="L547" s="16"/>
     </row>
-    <row r="548" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="548" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A548" s="1" t="s">
         <v>16</v>
       </c>
@@ -19858,7 +19855,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="549" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="549" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A549" s="1" t="s">
         <v>19</v>
       </c>
@@ -19884,7 +19881,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="550" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="550" spans="1:12" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A550" s="7" t="s">
         <v>22</v>
       </c>
@@ -19908,7 +19905,7 @@
       <c r="K550" s="16"/>
       <c r="L550" s="16"/>
     </row>
-    <row r="551" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="551" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A551" s="1" t="s">
         <v>16</v>
       </c>
@@ -19934,7 +19931,7 @@
         <v>0.32</v>
       </c>
     </row>
-    <row r="552" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="552" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A552" s="1" t="s">
         <v>19</v>
       </c>
@@ -19960,7 +19957,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="553" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="553" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A553" s="7" t="s">
         <v>22</v>
       </c>
@@ -19984,7 +19981,7 @@
       <c r="K553" s="16"/>
       <c r="L553" s="16"/>
     </row>
-    <row r="554" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="554" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A554" s="1" t="s">
         <v>19</v>
       </c>
@@ -20010,7 +20007,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="555" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="555" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A555" s="7" t="s">
         <v>22</v>
       </c>
@@ -20034,7 +20031,7 @@
       <c r="K555" s="16"/>
       <c r="L555" s="16"/>
     </row>
-    <row r="556" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="556" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A556" s="1" t="s">
         <v>16</v>
       </c>
@@ -20060,7 +20057,7 @@
         <v>0.17</v>
       </c>
     </row>
-    <row r="557" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="557" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A557" s="1" t="s">
         <v>19</v>
       </c>
@@ -20086,7 +20083,7 @@
         <v>0.17</v>
       </c>
     </row>
-    <row r="558" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="558" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A558" s="7" t="s">
         <v>22</v>
       </c>
@@ -20110,7 +20107,7 @@
       <c r="K558" s="16"/>
       <c r="L558" s="16"/>
     </row>
-    <row r="559" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="559" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A559" s="7" t="s">
         <v>22</v>
       </c>
@@ -20134,7 +20131,7 @@
       <c r="K559" s="16"/>
       <c r="L559" s="16"/>
     </row>
-    <row r="560" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="560" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A560" s="1" t="s">
         <v>13</v>
       </c>
@@ -20160,7 +20157,7 @@
         <v>2.08</v>
       </c>
     </row>
-    <row r="561" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="561" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A561" s="1" t="s">
         <v>16</v>
       </c>
@@ -20186,7 +20183,7 @@
         <v>0.95</v>
       </c>
     </row>
-    <row r="562" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="562" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A562" s="1" t="s">
         <v>19</v>
       </c>
@@ -20212,7 +20209,7 @@
         <v>0.43</v>
       </c>
     </row>
-    <row r="563" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="563" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A563" s="7" t="s">
         <v>22</v>
       </c>
@@ -20236,7 +20233,7 @@
       <c r="K563" s="16"/>
       <c r="L563" s="16"/>
     </row>
-    <row r="564" spans="1:12" ht="63.75" x14ac:dyDescent="0.25">
+    <row r="564" spans="1:12" ht="66" x14ac:dyDescent="0.3">
       <c r="A564" s="7" t="s">
         <v>22</v>
       </c>
@@ -20260,7 +20257,7 @@
       <c r="K564" s="16"/>
       <c r="L564" s="16"/>
     </row>
-    <row r="565" spans="1:12" ht="63.75" x14ac:dyDescent="0.25">
+    <row r="565" spans="1:12" ht="66" x14ac:dyDescent="0.3">
       <c r="A565" s="7" t="s">
         <v>22</v>
       </c>
@@ -20284,7 +20281,7 @@
       <c r="K565" s="16"/>
       <c r="L565" s="16"/>
     </row>
-    <row r="566" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="566" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A566" s="1" t="s">
         <v>19</v>
       </c>
@@ -20310,7 +20307,7 @@
         <v>0.52</v>
       </c>
     </row>
-    <row r="567" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="567" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A567" s="7" t="s">
         <v>22</v>
       </c>
@@ -20334,7 +20331,7 @@
       <c r="K567" s="16"/>
       <c r="L567" s="16"/>
     </row>
-    <row r="568" spans="1:12" ht="76.5" x14ac:dyDescent="0.25">
+    <row r="568" spans="1:12" ht="79.2" x14ac:dyDescent="0.3">
       <c r="A568" s="7" t="s">
         <v>22</v>
       </c>
@@ -20358,7 +20355,7 @@
       <c r="K568" s="16"/>
       <c r="L568" s="16"/>
     </row>
-    <row r="569" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="569" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A569" s="7" t="s">
         <v>22</v>
       </c>
@@ -20382,7 +20379,7 @@
       <c r="K569" s="16"/>
       <c r="L569" s="16"/>
     </row>
-    <row r="570" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="570" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A570" s="1" t="s">
         <v>16</v>
       </c>
@@ -20408,7 +20405,7 @@
         <v>1.1299999999999999</v>
       </c>
     </row>
-    <row r="571" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="571" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A571" s="1" t="s">
         <v>19</v>
       </c>
@@ -20434,7 +20431,7 @@
         <v>0.43</v>
       </c>
     </row>
-    <row r="572" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="572" spans="1:12" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A572" s="7" t="s">
         <v>22</v>
       </c>
@@ -20458,7 +20455,7 @@
       <c r="K572" s="16"/>
       <c r="L572" s="16"/>
     </row>
-    <row r="573" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="573" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A573" s="1" t="s">
         <v>19</v>
       </c>
@@ -20484,7 +20481,7 @@
         <v>0.69</v>
       </c>
     </row>
-    <row r="574" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="574" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A574" s="7" t="s">
         <v>22</v>
       </c>
@@ -20508,7 +20505,7 @@
       <c r="K574" s="16"/>
       <c r="L574" s="16"/>
     </row>
-    <row r="575" spans="1:12" ht="63.75" x14ac:dyDescent="0.25">
+    <row r="575" spans="1:12" ht="66" x14ac:dyDescent="0.3">
       <c r="A575" s="7" t="s">
         <v>22</v>
       </c>
@@ -20532,7 +20529,7 @@
       <c r="K575" s="16"/>
       <c r="L575" s="16"/>
     </row>
-    <row r="576" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="576" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A576" s="33" t="s">
         <v>22</v>
       </c>
@@ -20554,7 +20551,7 @@
       <c r="I576" s="5"/>
       <c r="J576" s="5"/>
     </row>
-    <row r="577" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="577" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A577" s="1" t="s">
         <v>13</v>
       </c>
@@ -20580,7 +20577,7 @@
         <v>0.44</v>
       </c>
     </row>
-    <row r="578" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="578" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A578" s="1" t="s">
         <v>16</v>
       </c>
@@ -20606,7 +20603,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="579" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="579" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A579" s="1" t="s">
         <v>19</v>
       </c>
@@ -20632,7 +20629,7 @@
         <v>0.13</v>
       </c>
     </row>
-    <row r="580" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="580" spans="1:12" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A580" s="7" t="s">
         <v>22</v>
       </c>
@@ -20656,7 +20653,7 @@
       <c r="K580" s="16"/>
       <c r="L580" s="16"/>
     </row>
-    <row r="581" spans="1:12" ht="51" x14ac:dyDescent="0.25">
+    <row r="581" spans="1:12" ht="52.8" x14ac:dyDescent="0.3">
       <c r="A581" s="7" t="s">
         <v>22</v>
       </c>
@@ -20680,7 +20677,7 @@
       <c r="K581" s="16"/>
       <c r="L581" s="16"/>
     </row>
-    <row r="582" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="582" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A582" s="1" t="s">
         <v>19</v>
       </c>
@@ -20706,7 +20703,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="583" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="583" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A583" s="7" t="s">
         <v>22</v>
       </c>
@@ -20730,7 +20727,7 @@
       <c r="K583" s="16"/>
       <c r="L583" s="16"/>
     </row>
-    <row r="584" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="584" spans="1:12" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A584" s="7" t="s">
         <v>22</v>
       </c>
@@ -20754,7 +20751,7 @@
       <c r="K584" s="16"/>
       <c r="L584" s="16"/>
     </row>
-    <row r="585" spans="1:12" ht="102" x14ac:dyDescent="0.25">
+    <row r="585" spans="1:12" ht="105.6" x14ac:dyDescent="0.3">
       <c r="A585" s="7" t="s">
         <v>22</v>
       </c>
@@ -20778,7 +20775,7 @@
       <c r="K585" s="16"/>
       <c r="L585" s="16"/>
     </row>
-    <row r="586" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="586" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A586" s="1" t="s">
         <v>16</v>
       </c>
@@ -20804,7 +20801,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="587" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="587" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A587" s="1" t="s">
         <v>19</v>
       </c>
@@ -20830,7 +20827,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="588" spans="1:12" ht="63.75" x14ac:dyDescent="0.25">
+    <row r="588" spans="1:12" ht="66" x14ac:dyDescent="0.3">
       <c r="A588" s="7" t="s">
         <v>22</v>
       </c>
@@ -20854,7 +20851,7 @@
       <c r="K588" s="16"/>
       <c r="L588" s="16"/>
     </row>
-    <row r="589" spans="1:12" ht="63.75" x14ac:dyDescent="0.25">
+    <row r="589" spans="1:12" ht="66" x14ac:dyDescent="0.3">
       <c r="A589" s="7" t="s">
         <v>22</v>
       </c>
@@ -20878,7 +20875,7 @@
       <c r="K589" s="16"/>
       <c r="L589" s="16"/>
     </row>
-    <row r="590" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="590" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A590" s="1" t="s">
         <v>16</v>
       </c>
@@ -20904,7 +20901,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="591" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="591" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A591" s="1" t="s">
         <v>19</v>
       </c>
@@ -20930,7 +20927,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="592" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="592" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A592" s="7" t="s">
         <v>22</v>
       </c>
@@ -20954,7 +20951,7 @@
       <c r="K592" s="16"/>
       <c r="L592" s="16"/>
     </row>
-    <row r="593" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="593" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A593" s="1" t="s">
         <v>16</v>
       </c>
@@ -20980,7 +20977,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="594" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="594" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A594" s="1" t="s">
         <v>19</v>
       </c>
@@ -21006,7 +21003,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="595" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="595" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A595" s="7" t="s">
         <v>22</v>
       </c>
@@ -21030,7 +21027,7 @@
       <c r="K595" s="16"/>
       <c r="L595" s="16"/>
     </row>
-    <row r="596" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="596" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A596" s="7" t="s">
         <v>22</v>
       </c>
@@ -21054,7 +21051,7 @@
       <c r="K596" s="16"/>
       <c r="L596" s="16"/>
     </row>
-    <row r="597" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="597" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A597" s="7" t="s">
         <v>22</v>
       </c>
@@ -21078,7 +21075,7 @@
       <c r="K597" s="16"/>
       <c r="L597" s="16"/>
     </row>
-    <row r="598" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="598" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A598" s="1" t="s">
         <v>19</v>
       </c>
@@ -21104,7 +21101,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="599" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="599" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A599" s="7" t="s">
         <v>22</v>
       </c>
@@ -21128,7 +21125,7 @@
       <c r="K599" s="16"/>
       <c r="L599" s="16"/>
     </row>
-    <row r="600" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="600" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A600" s="7" t="s">
         <v>22</v>
       </c>
@@ -21152,7 +21149,7 @@
       <c r="K600" s="16"/>
       <c r="L600" s="16"/>
     </row>
-    <row r="601" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="601" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A601" s="1" t="s">
         <v>19</v>
       </c>
@@ -21178,7 +21175,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="602" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="602" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A602" s="7" t="s">
         <v>22</v>
       </c>
@@ -21202,7 +21199,7 @@
       <c r="K602" s="16"/>
       <c r="L602" s="16"/>
     </row>
-    <row r="603" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="603" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A603" s="7" t="s">
         <v>22</v>
       </c>
@@ -21226,7 +21223,7 @@
       <c r="K603" s="16"/>
       <c r="L603" s="16"/>
     </row>
-    <row r="604" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="604" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A604" s="1" t="s">
         <v>13</v>
       </c>
@@ -21252,7 +21249,7 @@
         <v>1.26</v>
       </c>
     </row>
-    <row r="605" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="605" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A605" s="1" t="s">
         <v>16</v>
       </c>
@@ -21278,7 +21275,7 @@
         <v>1.26</v>
       </c>
     </row>
-    <row r="606" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="606" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A606" s="1" t="s">
         <v>19</v>
       </c>
@@ -21304,7 +21301,7 @@
         <v>1.26</v>
       </c>
     </row>
-    <row r="607" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="607" spans="1:12" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A607" s="7" t="s">
         <v>22</v>
       </c>
@@ -21328,7 +21325,7 @@
       <c r="K607" s="16"/>
       <c r="L607" s="16"/>
     </row>
-    <row r="608" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="608" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A608" s="7" t="s">
         <v>22</v>
       </c>
@@ -21352,7 +21349,7 @@
       <c r="K608" s="16"/>
       <c r="L608" s="16"/>
     </row>
-    <row r="609" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="609" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A609" s="7" t="s">
         <v>22</v>
       </c>
@@ -21376,7 +21373,7 @@
       <c r="K609" s="16"/>
       <c r="L609" s="16"/>
     </row>
-    <row r="610" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="610" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A610" s="1" t="s">
         <v>10</v>
       </c>
@@ -21402,7 +21399,7 @@
         <v>6.55</v>
       </c>
     </row>
-    <row r="611" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="611" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A611" s="1" t="s">
         <v>13</v>
       </c>
@@ -21428,7 +21425,7 @@
         <v>2.4500000000000002</v>
       </c>
     </row>
-    <row r="612" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="612" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A612" s="1" t="s">
         <v>16</v>
       </c>
@@ -21454,7 +21451,7 @@
         <v>2.4500000000000002</v>
       </c>
     </row>
-    <row r="613" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="613" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A613" s="1" t="s">
         <v>19</v>
       </c>
@@ -21480,7 +21477,7 @@
         <v>2.4500000000000002</v>
       </c>
     </row>
-    <row r="614" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="614" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A614" s="7" t="s">
         <v>22</v>
       </c>
@@ -21504,7 +21501,7 @@
       <c r="K614" s="16"/>
       <c r="L614" s="16"/>
     </row>
-    <row r="615" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="615" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A615" s="7" t="s">
         <v>22</v>
       </c>
@@ -21528,7 +21525,7 @@
       <c r="K615" s="16"/>
       <c r="L615" s="16"/>
     </row>
-    <row r="616" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="616" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A616" s="7" t="s">
         <v>22</v>
       </c>
@@ -21552,7 +21549,7 @@
       <c r="K616" s="16"/>
       <c r="L616" s="16"/>
     </row>
-    <row r="617" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="617" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A617" s="7" t="s">
         <v>22</v>
       </c>
@@ -21576,7 +21573,7 @@
       <c r="K617" s="16"/>
       <c r="L617" s="16"/>
     </row>
-    <row r="618" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="618" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A618" s="1" t="s">
         <v>13</v>
       </c>
@@ -21602,7 +21599,7 @@
         <v>1.33</v>
       </c>
     </row>
-    <row r="619" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="619" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A619" s="1" t="s">
         <v>16</v>
       </c>
@@ -21628,7 +21625,7 @@
         <v>1.33</v>
       </c>
     </row>
-    <row r="620" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="620" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A620" s="1" t="s">
         <v>19</v>
       </c>
@@ -21654,7 +21651,7 @@
         <v>1.33</v>
       </c>
     </row>
-    <row r="621" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="621" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A621" s="7" t="s">
         <v>22</v>
       </c>
@@ -21678,7 +21675,7 @@
       <c r="K621" s="16"/>
       <c r="L621" s="16"/>
     </row>
-    <row r="622" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="622" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A622" s="7" t="s">
         <v>22</v>
       </c>
@@ -21702,7 +21699,7 @@
       <c r="K622" s="16"/>
       <c r="L622" s="16"/>
     </row>
-    <row r="623" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="623" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A623" s="1" t="s">
         <v>13</v>
       </c>
@@ -21728,7 +21725,7 @@
         <v>2.29</v>
       </c>
     </row>
-    <row r="624" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="624" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A624" s="1" t="s">
         <v>16</v>
       </c>
@@ -21754,7 +21751,7 @@
         <v>2.29</v>
       </c>
     </row>
-    <row r="625" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="625" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A625" s="1" t="s">
         <v>19</v>
       </c>
@@ -21780,7 +21777,7 @@
         <v>1.41</v>
       </c>
     </row>
-    <row r="626" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="626" spans="1:12" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A626" s="7" t="s">
         <v>22</v>
       </c>
@@ -21804,7 +21801,7 @@
       <c r="K626" s="16"/>
       <c r="L626" s="16"/>
     </row>
-    <row r="627" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="627" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A627" s="7" t="s">
         <v>22</v>
       </c>
@@ -21828,7 +21825,7 @@
       <c r="K627" s="16"/>
       <c r="L627" s="16"/>
     </row>
-    <row r="628" spans="1:12" ht="63.75" x14ac:dyDescent="0.25">
+    <row r="628" spans="1:12" ht="66" x14ac:dyDescent="0.3">
       <c r="A628" s="7" t="s">
         <v>22</v>
       </c>
@@ -21852,7 +21849,7 @@
       <c r="K628" s="16"/>
       <c r="L628" s="16"/>
     </row>
-    <row r="629" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="629" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A629" s="1" t="s">
         <v>19</v>
       </c>
@@ -21878,7 +21875,7 @@
         <v>0.65</v>
       </c>
     </row>
-    <row r="630" spans="1:12" ht="51" x14ac:dyDescent="0.25">
+    <row r="630" spans="1:12" ht="52.8" x14ac:dyDescent="0.3">
       <c r="A630" s="9" t="s">
         <v>22</v>
       </c>
@@ -21902,7 +21899,7 @@
       <c r="K630" s="13"/>
       <c r="L630" s="13"/>
     </row>
-    <row r="631" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="631" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A631" s="9" t="s">
         <v>22</v>
       </c>
@@ -21926,7 +21923,7 @@
       <c r="K631" s="13"/>
       <c r="L631" s="13"/>
     </row>
-    <row r="632" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="632" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A632" s="1" t="s">
         <v>19</v>
       </c>
@@ -21952,7 +21949,7 @@
         <v>0.23</v>
       </c>
     </row>
-    <row r="633" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="633" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A633" s="7" t="s">
         <v>22</v>
       </c>
@@ -21976,7 +21973,7 @@
       <c r="K633" s="16"/>
       <c r="L633" s="16"/>
     </row>
-    <row r="634" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="634" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A634" s="1" t="s">
         <v>13</v>
       </c>
@@ -22002,7 +21999,7 @@
         <v>0.49</v>
       </c>
     </row>
-    <row r="635" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="635" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A635" s="1" t="s">
         <v>16</v>
       </c>
@@ -22028,7 +22025,7 @@
         <v>0.49</v>
       </c>
     </row>
-    <row r="636" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="636" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A636" s="1" t="s">
         <v>19</v>
       </c>
@@ -22054,7 +22051,7 @@
         <v>0.39</v>
       </c>
     </row>
-    <row r="637" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="637" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A637" s="7" t="s">
         <v>22</v>
       </c>
@@ -22078,7 +22075,7 @@
       <c r="K637" s="16"/>
       <c r="L637" s="16"/>
     </row>
-    <row r="638" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="638" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A638" s="7" t="s">
         <v>22</v>
       </c>
@@ -22102,7 +22099,7 @@
       <c r="K638" s="16"/>
       <c r="L638" s="16"/>
     </row>
-    <row r="639" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="639" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A639" s="1" t="s">
         <v>19</v>
       </c>
@@ -22128,7 +22125,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="640" spans="1:12" ht="63.75" x14ac:dyDescent="0.25">
+    <row r="640" spans="1:12" ht="66" x14ac:dyDescent="0.3">
       <c r="A640" s="7" t="s">
         <v>22</v>
       </c>
@@ -22152,7 +22149,7 @@
       <c r="K640" s="16"/>
       <c r="L640" s="16"/>
     </row>
-    <row r="641" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="641" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A641" s="1" t="s">
         <v>19</v>
       </c>
@@ -22178,7 +22175,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="642" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="642" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A642" s="7" t="s">
         <v>22</v>
       </c>
@@ -22202,7 +22199,7 @@
       <c r="K642" s="16"/>
       <c r="L642" s="16"/>
     </row>
-    <row r="643" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="643" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A643" s="1" t="s">
         <v>10</v>
       </c>
@@ -22228,7 +22225,7 @@
         <v>10.31</v>
       </c>
     </row>
-    <row r="644" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="644" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A644" s="1" t="s">
         <v>13</v>
       </c>
@@ -22254,7 +22251,7 @@
         <v>9.69</v>
       </c>
     </row>
-    <row r="645" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="645" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A645" s="1" t="s">
         <v>16</v>
       </c>
@@ -22280,7 +22277,7 @@
         <v>9.4700000000000006</v>
       </c>
     </row>
-    <row r="646" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="646" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A646" s="1" t="s">
         <v>19</v>
       </c>
@@ -22306,7 +22303,7 @@
         <v>7.23</v>
       </c>
     </row>
-    <row r="647" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="647" spans="1:12" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A647" s="7" t="s">
         <v>22</v>
       </c>
@@ -22330,7 +22327,7 @@
       <c r="K647" s="16"/>
       <c r="L647" s="16"/>
     </row>
-    <row r="648" spans="1:12" ht="51" x14ac:dyDescent="0.25">
+    <row r="648" spans="1:12" ht="52.8" x14ac:dyDescent="0.3">
       <c r="A648" s="7" t="s">
         <v>22</v>
       </c>
@@ -22354,7 +22351,7 @@
       <c r="K648" s="16"/>
       <c r="L648" s="16"/>
     </row>
-    <row r="649" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="649" spans="1:12" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A649" s="7" t="s">
         <v>22</v>
       </c>
@@ -22378,7 +22375,7 @@
       <c r="K649" s="16"/>
       <c r="L649" s="16"/>
     </row>
-    <row r="650" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="650" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A650" s="1" t="s">
         <v>19</v>
       </c>
@@ -22404,7 +22401,7 @@
         <v>0.17</v>
       </c>
     </row>
-    <row r="651" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="651" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A651" s="7" t="s">
         <v>22</v>
       </c>
@@ -22428,7 +22425,7 @@
       <c r="K651" s="16"/>
       <c r="L651" s="16"/>
     </row>
-    <row r="652" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="652" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A652" s="1" t="s">
         <v>19</v>
       </c>
@@ -22454,7 +22451,7 @@
         <v>0.13</v>
       </c>
     </row>
-    <row r="653" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="653" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A653" s="7" t="s">
         <v>22</v>
       </c>
@@ -22478,7 +22475,7 @@
       <c r="K653" s="16"/>
       <c r="L653" s="16"/>
     </row>
-    <row r="654" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="654" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A654" s="7" t="s">
         <v>22</v>
       </c>
@@ -22502,7 +22499,7 @@
       <c r="K654" s="16"/>
       <c r="L654" s="16"/>
     </row>
-    <row r="655" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="655" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A655" s="1" t="s">
         <v>19</v>
       </c>
@@ -22528,7 +22525,7 @@
         <v>1.35</v>
       </c>
     </row>
-    <row r="656" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="656" spans="1:12" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A656" s="7" t="s">
         <v>22</v>
       </c>
@@ -22552,7 +22549,7 @@
       <c r="K656" s="16"/>
       <c r="L656" s="16"/>
     </row>
-    <row r="657" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="657" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A657" s="7" t="s">
         <v>22</v>
       </c>
@@ -22576,7 +22573,7 @@
       <c r="K657" s="16"/>
       <c r="L657" s="16"/>
     </row>
-    <row r="658" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="658" spans="1:12" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A658" s="7" t="s">
         <v>22</v>
       </c>
@@ -22600,7 +22597,7 @@
       <c r="K658" s="16"/>
       <c r="L658" s="16"/>
     </row>
-    <row r="659" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="659" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A659" s="7" t="s">
         <v>22</v>
       </c>
@@ -22624,7 +22621,7 @@
       <c r="K659" s="16"/>
       <c r="L659" s="16"/>
     </row>
-    <row r="660" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="660" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A660" s="7" t="s">
         <v>22</v>
       </c>
@@ -22648,7 +22645,7 @@
       <c r="K660" s="16"/>
       <c r="L660" s="16"/>
     </row>
-    <row r="661" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="661" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A661" s="7" t="s">
         <v>22</v>
       </c>
@@ -22672,7 +22669,7 @@
       <c r="K661" s="16"/>
       <c r="L661" s="16"/>
     </row>
-    <row r="662" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="662" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A662" s="7" t="s">
         <v>22</v>
       </c>
@@ -22696,7 +22693,7 @@
       <c r="K662" s="16"/>
       <c r="L662" s="16"/>
     </row>
-    <row r="663" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="663" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A663" s="7" t="s">
         <v>22</v>
       </c>
@@ -22720,7 +22717,7 @@
       <c r="K663" s="16"/>
       <c r="L663" s="16"/>
     </row>
-    <row r="664" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="664" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A664" s="1" t="s">
         <v>19</v>
       </c>
@@ -22746,7 +22743,7 @@
         <v>0.57999999999999996</v>
       </c>
     </row>
-    <row r="665" spans="1:12" ht="51" x14ac:dyDescent="0.25">
+    <row r="665" spans="1:12" ht="52.8" x14ac:dyDescent="0.3">
       <c r="A665" s="7" t="s">
         <v>22</v>
       </c>
@@ -22770,7 +22767,7 @@
       <c r="K665" s="16"/>
       <c r="L665" s="16"/>
     </row>
-    <row r="666" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="666" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A666" s="1" t="s">
         <v>16</v>
       </c>
@@ -22796,7 +22793,7 @@
         <v>0.22</v>
       </c>
     </row>
-    <row r="667" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="667" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A667" s="1" t="s">
         <v>19</v>
       </c>
@@ -22822,7 +22819,7 @@
         <v>0.22</v>
       </c>
     </row>
-    <row r="668" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="668" spans="1:12" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A668" s="7" t="s">
         <v>22</v>
       </c>
@@ -22846,7 +22843,7 @@
       <c r="K668" s="16"/>
       <c r="L668" s="16"/>
     </row>
-    <row r="669" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="669" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A669" s="1" t="s">
         <v>13</v>
       </c>
@@ -22872,7 +22869,7 @@
         <v>0.61</v>
       </c>
     </row>
-    <row r="670" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="670" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A670" s="1" t="s">
         <v>16</v>
       </c>
@@ -22898,7 +22895,7 @@
         <v>0.61</v>
       </c>
     </row>
-    <row r="671" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="671" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A671" s="1" t="s">
         <v>19</v>
       </c>
@@ -22924,7 +22921,7 @@
         <v>0.61</v>
       </c>
     </row>
-    <row r="672" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="672" spans="1:12" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A672" s="7" t="s">
         <v>22</v>
       </c>
@@ -22948,7 +22945,7 @@
       <c r="K672" s="16"/>
       <c r="L672" s="16"/>
     </row>
-    <row r="673" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="673" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A673" s="1" t="s">
         <v>10</v>
       </c>
@@ -22974,7 +22971,7 @@
         <v>5.32</v>
       </c>
     </row>
-    <row r="674" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="674" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A674" s="1" t="s">
         <v>13</v>
       </c>
@@ -23000,7 +22997,7 @@
         <v>3.24</v>
       </c>
     </row>
-    <row r="675" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="675" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A675" s="1" t="s">
         <v>16</v>
       </c>
@@ -23026,7 +23023,7 @@
         <v>0.88</v>
       </c>
     </row>
-    <row r="676" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="676" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A676" s="1" t="s">
         <v>19</v>
       </c>
@@ -23052,7 +23049,7 @@
         <v>0.88</v>
       </c>
     </row>
-    <row r="677" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="677" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A677" s="7" t="s">
         <v>22</v>
       </c>
@@ -23076,7 +23073,7 @@
       <c r="K677" s="16"/>
       <c r="L677" s="16"/>
     </row>
-    <row r="678" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="678" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A678" s="7" t="s">
         <v>22</v>
       </c>
@@ -23100,7 +23097,7 @@
       <c r="K678" s="16"/>
       <c r="L678" s="16"/>
     </row>
-    <row r="679" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="679" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A679" s="1" t="s">
         <v>16</v>
       </c>
@@ -23126,7 +23123,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="680" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="680" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A680" s="1" t="s">
         <v>19</v>
       </c>
@@ -23152,7 +23149,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="681" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="681" spans="1:12" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A681" s="7" t="s">
         <v>22</v>
       </c>
@@ -23176,7 +23173,7 @@
       <c r="K681" s="16"/>
       <c r="L681" s="16"/>
     </row>
-    <row r="682" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="682" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A682" s="7" t="s">
         <v>22</v>
       </c>
@@ -23200,7 +23197,7 @@
       <c r="K682" s="16"/>
       <c r="L682" s="16"/>
     </row>
-    <row r="683" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="683" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A683" s="1" t="s">
         <v>16</v>
       </c>
@@ -23226,7 +23223,7 @@
         <v>2.35</v>
       </c>
     </row>
-    <row r="684" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="684" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A684" s="1" t="s">
         <v>19</v>
       </c>
@@ -23252,7 +23249,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="685" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="685" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A685" s="7" t="s">
         <v>22</v>
       </c>
@@ -23276,7 +23273,7 @@
       <c r="K685" s="16"/>
       <c r="L685" s="16"/>
     </row>
-    <row r="686" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="686" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A686" s="1" t="s">
         <v>19</v>
       </c>
@@ -23302,7 +23299,7 @@
         <v>1.1200000000000001</v>
       </c>
     </row>
-    <row r="687" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="687" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A687" s="7" t="s">
         <v>22</v>
       </c>
@@ -23326,7 +23323,7 @@
       <c r="K687" s="16"/>
       <c r="L687" s="16"/>
     </row>
-    <row r="688" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="688" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A688" s="7" t="s">
         <v>22</v>
       </c>
@@ -23350,7 +23347,7 @@
       <c r="K688" s="16"/>
       <c r="L688" s="16"/>
     </row>
-    <row r="689" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="689" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A689" s="7" t="s">
         <v>22</v>
       </c>
@@ -23374,7 +23371,7 @@
       <c r="K689" s="16"/>
       <c r="L689" s="16"/>
     </row>
-    <row r="690" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="690" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A690" s="7" t="s">
         <v>22</v>
       </c>
@@ -23398,7 +23395,7 @@
       <c r="K690" s="16"/>
       <c r="L690" s="16"/>
     </row>
-    <row r="691" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="691" spans="1:12" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A691" s="7" t="s">
         <v>22</v>
       </c>
@@ -23422,7 +23419,7 @@
       <c r="K691" s="16"/>
       <c r="L691" s="16"/>
     </row>
-    <row r="692" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="692" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A692" s="1" t="s">
         <v>19</v>
       </c>
@@ -23448,7 +23445,7 @@
         <v>0.26</v>
       </c>
     </row>
-    <row r="693" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="693" spans="1:12" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A693" s="7" t="s">
         <v>22</v>
       </c>
@@ -23472,7 +23469,7 @@
       <c r="K693" s="16"/>
       <c r="L693" s="16"/>
     </row>
-    <row r="694" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="694" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A694" s="7" t="s">
         <v>22</v>
       </c>
@@ -23496,7 +23493,7 @@
       <c r="K694" s="16"/>
       <c r="L694" s="16"/>
     </row>
-    <row r="695" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="695" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A695" s="7" t="s">
         <v>22</v>
       </c>
@@ -23520,7 +23517,7 @@
       <c r="K695" s="16"/>
       <c r="L695" s="16"/>
     </row>
-    <row r="696" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="696" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A696" s="1" t="s">
         <v>19</v>
       </c>
@@ -23546,7 +23543,7 @@
         <v>0.39</v>
       </c>
     </row>
-    <row r="697" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="697" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A697" s="7" t="s">
         <v>22</v>
       </c>
@@ -23570,7 +23567,7 @@
       <c r="K697" s="16"/>
       <c r="L697" s="16"/>
     </row>
-    <row r="698" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="698" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A698" s="7" t="s">
         <v>22</v>
       </c>
@@ -23594,7 +23591,7 @@
       <c r="K698" s="16"/>
       <c r="L698" s="16"/>
     </row>
-    <row r="699" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="699" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A699" s="7" t="s">
         <v>22</v>
       </c>
@@ -23618,7 +23615,7 @@
       <c r="K699" s="16"/>
       <c r="L699" s="16"/>
     </row>
-    <row r="700" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="700" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A700" s="7" t="s">
         <v>22</v>
       </c>
@@ -23642,7 +23639,7 @@
       <c r="K700" s="16"/>
       <c r="L700" s="16"/>
     </row>
-    <row r="701" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="701" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A701" s="1" t="s">
         <v>19</v>
       </c>
@@ -23668,7 +23665,7 @@
         <v>0.51</v>
       </c>
     </row>
-    <row r="702" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="702" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A702" s="7" t="s">
         <v>22</v>
       </c>
@@ -23692,7 +23689,7 @@
       <c r="K702" s="16"/>
       <c r="L702" s="16"/>
     </row>
-    <row r="703" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="703" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A703" s="7" t="s">
         <v>22</v>
       </c>
@@ -23716,7 +23713,7 @@
       <c r="K703" s="16"/>
       <c r="L703" s="16"/>
     </row>
-    <row r="704" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="704" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A704" s="7" t="s">
         <v>22</v>
       </c>
@@ -23740,7 +23737,7 @@
       <c r="K704" s="16"/>
       <c r="L704" s="16"/>
     </row>
-    <row r="705" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="705" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A705" s="1" t="s">
         <v>13</v>
       </c>
@@ -23766,7 +23763,7 @@
         <v>0.45</v>
       </c>
     </row>
-    <row r="706" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="706" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A706" s="1" t="s">
         <v>16</v>
       </c>
@@ -23792,7 +23789,7 @@
         <v>0.26</v>
       </c>
     </row>
-    <row r="707" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="707" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A707" s="1" t="s">
         <v>19</v>
       </c>
@@ -23818,7 +23815,7 @@
         <v>0.14000000000000001</v>
       </c>
     </row>
-    <row r="708" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="708" spans="1:12" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A708" s="7" t="s">
         <v>22</v>
       </c>
@@ -23842,7 +23839,7 @@
       <c r="K708" s="16"/>
       <c r="L708" s="16"/>
     </row>
-    <row r="709" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="709" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A709" s="1" t="s">
         <v>19</v>
       </c>
@@ -23868,7 +23865,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="710" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="710" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A710" s="7" t="s">
         <v>22</v>
       </c>
@@ -23892,7 +23889,7 @@
       <c r="K710" s="16"/>
       <c r="L710" s="16"/>
     </row>
-    <row r="711" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="711" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A711" s="1" t="s">
         <v>19</v>
       </c>
@@ -23918,7 +23915,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="712" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="712" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A712" s="7" t="s">
         <v>22</v>
       </c>
@@ -23942,7 +23939,7 @@
       <c r="K712" s="16"/>
       <c r="L712" s="16"/>
     </row>
-    <row r="713" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="713" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A713" s="1" t="s">
         <v>16</v>
       </c>
@@ -23968,7 +23965,7 @@
         <v>0.19</v>
       </c>
     </row>
-    <row r="714" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="714" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A714" s="1" t="s">
         <v>19</v>
       </c>
@@ -23994,7 +23991,7 @@
         <v>0.11</v>
       </c>
     </row>
-    <row r="715" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="715" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A715" s="7" t="s">
         <v>22</v>
       </c>
@@ -24018,7 +24015,7 @@
       <c r="K715" s="16"/>
       <c r="L715" s="16"/>
     </row>
-    <row r="716" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="716" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A716" s="7" t="s">
         <v>22</v>
       </c>
@@ -24042,7 +24039,7 @@
       <c r="K716" s="16"/>
       <c r="L716" s="16"/>
     </row>
-    <row r="717" spans="1:12" ht="51" x14ac:dyDescent="0.25">
+    <row r="717" spans="1:12" ht="52.8" x14ac:dyDescent="0.3">
       <c r="A717" s="7" t="s">
         <v>22</v>
       </c>
@@ -24066,7 +24063,7 @@
       <c r="K717" s="16"/>
       <c r="L717" s="16"/>
     </row>
-    <row r="718" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="718" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A718" s="1" t="s">
         <v>19</v>
       </c>
@@ -24092,7 +24089,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="719" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="719" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A719" s="7" t="s">
         <v>22</v>
       </c>
@@ -24116,7 +24113,7 @@
       <c r="K719" s="16"/>
       <c r="L719" s="16"/>
     </row>
-    <row r="720" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="720" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A720" s="1" t="s">
         <v>19</v>
       </c>
@@ -24142,7 +24139,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="721" spans="1:12" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="721" spans="1:12" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A721" s="7" t="s">
         <v>22</v>
       </c>
@@ -24166,7 +24163,7 @@
       <c r="K721" s="16"/>
       <c r="L721" s="16"/>
     </row>
-    <row r="722" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="722" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A722" s="1" t="s">
         <v>13</v>
       </c>
@@ -24192,7 +24189,7 @@
         <v>0.47</v>
       </c>
     </row>
-    <row r="723" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="723" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A723" s="1" t="s">
         <v>16</v>
       </c>
@@ -24218,7 +24215,7 @@
         <v>0.47</v>
       </c>
     </row>
-    <row r="724" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="724" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A724" s="1" t="s">
         <v>19</v>
       </c>
@@ -24244,7 +24241,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="725" spans="1:12" ht="51" x14ac:dyDescent="0.25">
+    <row r="725" spans="1:12" ht="52.8" x14ac:dyDescent="0.3">
       <c r="A725" s="7" t="s">
         <v>22</v>
       </c>
@@ -24268,7 +24265,7 @@
       <c r="K725" s="16"/>
       <c r="L725" s="16"/>
     </row>
-    <row r="726" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="726" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A726" s="1" t="s">
         <v>19</v>
       </c>
@@ -24294,7 +24291,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="727" spans="1:12" ht="63.75" x14ac:dyDescent="0.25">
+    <row r="727" spans="1:12" ht="66" x14ac:dyDescent="0.3">
       <c r="A727" s="7" t="s">
         <v>22</v>
       </c>
@@ -24318,7 +24315,7 @@
       <c r="K727" s="16"/>
       <c r="L727" s="16"/>
     </row>
-    <row r="728" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="728" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A728" s="1" t="s">
         <v>19</v>
       </c>
@@ -24344,7 +24341,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="729" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="729" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A729" s="7" t="s">
         <v>22</v>
       </c>
@@ -24368,7 +24365,7 @@
       <c r="K729" s="16"/>
       <c r="L729" s="16"/>
     </row>
-    <row r="730" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="730" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A730" s="1" t="s">
         <v>13</v>
       </c>
@@ -24394,7 +24391,7 @@
         <v>0.73</v>
       </c>
     </row>
-    <row r="731" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="731" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A731" s="1" t="s">
         <v>16</v>
       </c>
@@ -24420,7 +24417,7 @@
         <v>0.35</v>
       </c>
     </row>
-    <row r="732" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="732" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A732" s="1" t="s">
         <v>19</v>
       </c>
@@ -24446,7 +24443,7 @@
         <v>0.35</v>
       </c>
     </row>
-    <row r="733" spans="1:12" ht="89.25" x14ac:dyDescent="0.25">
+    <row r="733" spans="1:12" ht="92.4" x14ac:dyDescent="0.3">
       <c r="A733" s="7" t="s">
         <v>22</v>
       </c>
@@ -24470,7 +24467,7 @@
       <c r="K733" s="16"/>
       <c r="L733" s="16"/>
     </row>
-    <row r="734" spans="1:12" ht="63.75" x14ac:dyDescent="0.25">
+    <row r="734" spans="1:12" ht="66" x14ac:dyDescent="0.3">
       <c r="A734" s="7" t="s">
         <v>22</v>
       </c>
@@ -24494,7 +24491,7 @@
       <c r="K734" s="16"/>
       <c r="L734" s="16"/>
     </row>
-    <row r="735" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="735" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A735" s="1" t="s">
         <v>16</v>
       </c>
@@ -24520,7 +24517,7 @@
         <v>0.38</v>
       </c>
     </row>
-    <row r="736" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="736" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A736" s="1" t="s">
         <v>19</v>
       </c>
@@ -24546,7 +24543,7 @@
         <v>0.38</v>
       </c>
     </row>
-    <row r="737" spans="1:12" ht="63.75" x14ac:dyDescent="0.25">
+    <row r="737" spans="1:12" ht="66" x14ac:dyDescent="0.3">
       <c r="A737" s="7" t="s">
         <v>22</v>
       </c>
@@ -24570,7 +24567,7 @@
       <c r="K737" s="16"/>
       <c r="L737" s="16"/>
     </row>
-    <row r="738" spans="1:12" ht="76.5" x14ac:dyDescent="0.25">
+    <row r="738" spans="1:12" ht="79.2" x14ac:dyDescent="0.3">
       <c r="A738" s="7" t="s">
         <v>22</v>
       </c>
@@ -24594,7 +24591,7 @@
       <c r="K738" s="16"/>
       <c r="L738" s="16"/>
     </row>
-    <row r="739" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="739" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A739" s="1" t="s">
         <v>13</v>
       </c>
@@ -24620,7 +24617,7 @@
         <v>0.28999999999999998</v>
       </c>
     </row>
-    <row r="740" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="740" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A740" s="1" t="s">
         <v>16</v>
       </c>
@@ -24646,7 +24643,7 @@
         <v>0.28999999999999998</v>
       </c>
     </row>
-    <row r="741" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="741" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A741" s="1" t="s">
         <v>19</v>
       </c>
@@ -24672,7 +24669,7 @@
         <v>0.28999999999999998</v>
       </c>
     </row>
-    <row r="742" spans="1:12" ht="102" x14ac:dyDescent="0.25">
+    <row r="742" spans="1:12" ht="105.6" x14ac:dyDescent="0.3">
       <c r="A742" s="7" t="s">
         <v>22</v>
       </c>
@@ -24696,7 +24693,7 @@
       <c r="K742" s="16"/>
       <c r="L742" s="16"/>
     </row>
-    <row r="743" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="743" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A743" s="7" t="s">
         <v>22</v>
       </c>
@@ -24720,7 +24717,7 @@
       <c r="K743" s="16"/>
       <c r="L743" s="16"/>
     </row>
-    <row r="744" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="744" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A744" s="1" t="s">
         <v>13</v>
       </c>
@@ -24746,7 +24743,7 @@
         <v>0.13</v>
       </c>
     </row>
-    <row r="745" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="745" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A745" s="1" t="s">
         <v>16</v>
       </c>
@@ -24772,7 +24769,7 @@
         <v>0.13</v>
       </c>
     </row>
-    <row r="746" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="746" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A746" s="1" t="s">
         <v>19</v>
       </c>
@@ -24798,7 +24795,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="747" spans="1:12" ht="51" x14ac:dyDescent="0.25">
+    <row r="747" spans="1:12" ht="52.8" x14ac:dyDescent="0.3">
       <c r="A747" s="7" t="s">
         <v>22</v>
       </c>
@@ -24822,7 +24819,7 @@
       <c r="K747" s="16"/>
       <c r="L747" s="16"/>
     </row>
-    <row r="748" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="748" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A748" s="1" t="s">
         <v>19</v>
       </c>
@@ -24848,7 +24845,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="749" spans="1:12" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="749" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A749" s="41" t="s">
         <v>22</v>
       </c>
@@ -24872,7 +24869,7 @@
       <c r="K749" s="16"/>
       <c r="L749" s="16"/>
     </row>
-    <row r="751" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="751" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A751" s="46" t="s">
         <v>1872</v>
       </c>
@@ -24885,131 +24882,131 @@
       <c r="H751" s="49"/>
       <c r="I751" s="49"/>
     </row>
-    <row r="752" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A752" s="50" t="s">
+    <row r="752" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A752" s="54" t="s">
         <v>1873</v>
       </c>
-      <c r="B752" s="50"/>
-      <c r="C752" s="50"/>
-      <c r="D752" s="50"/>
-      <c r="E752" s="50"/>
-      <c r="F752" s="50"/>
-      <c r="G752" s="50"/>
-      <c r="H752" s="50"/>
-      <c r="I752" s="50"/>
-    </row>
-    <row r="753" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A753" s="50"/>
-      <c r="B753" s="50"/>
-      <c r="C753" s="50"/>
-      <c r="D753" s="50"/>
-      <c r="E753" s="50"/>
-      <c r="F753" s="50"/>
-      <c r="G753" s="50"/>
-      <c r="H753" s="50"/>
-      <c r="I753" s="50"/>
-    </row>
-    <row r="754" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A754" s="51" t="s">
+      <c r="B752" s="54"/>
+      <c r="C752" s="54"/>
+      <c r="D752" s="54"/>
+      <c r="E752" s="54"/>
+      <c r="F752" s="54"/>
+      <c r="G752" s="54"/>
+      <c r="H752" s="54"/>
+      <c r="I752" s="54"/>
+    </row>
+    <row r="753" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A753" s="54"/>
+      <c r="B753" s="54"/>
+      <c r="C753" s="54"/>
+      <c r="D753" s="54"/>
+      <c r="E753" s="54"/>
+      <c r="F753" s="54"/>
+      <c r="G753" s="54"/>
+      <c r="H753" s="54"/>
+      <c r="I753" s="54"/>
+    </row>
+    <row r="754" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A754" s="54" t="s">
         <v>1874</v>
       </c>
-      <c r="B754" s="51"/>
-      <c r="C754" s="51"/>
-      <c r="D754" s="51"/>
-      <c r="E754" s="51"/>
-      <c r="F754" s="51"/>
-      <c r="G754" s="51"/>
-      <c r="H754" s="51"/>
-      <c r="I754" s="51"/>
-      <c r="J754" s="51"/>
-    </row>
-    <row r="755" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A755" s="51"/>
-      <c r="B755" s="51"/>
-      <c r="C755" s="51"/>
-      <c r="D755" s="51"/>
-      <c r="E755" s="51"/>
-      <c r="F755" s="51"/>
-      <c r="G755" s="51"/>
-      <c r="H755" s="51"/>
-      <c r="I755" s="51"/>
-      <c r="J755" s="51"/>
-    </row>
-    <row r="756" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A756" s="51"/>
-      <c r="B756" s="51"/>
-      <c r="C756" s="51"/>
-      <c r="D756" s="51"/>
-      <c r="E756" s="51"/>
-      <c r="F756" s="51"/>
-      <c r="G756" s="51"/>
-      <c r="H756" s="51"/>
-      <c r="I756" s="51"/>
-      <c r="J756" s="51"/>
-    </row>
-    <row r="757" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A757" s="51" t="s">
+      <c r="B754" s="54"/>
+      <c r="C754" s="54"/>
+      <c r="D754" s="54"/>
+      <c r="E754" s="54"/>
+      <c r="F754" s="54"/>
+      <c r="G754" s="54"/>
+      <c r="H754" s="54"/>
+      <c r="I754" s="54"/>
+      <c r="J754" s="54"/>
+    </row>
+    <row r="755" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A755" s="54"/>
+      <c r="B755" s="54"/>
+      <c r="C755" s="54"/>
+      <c r="D755" s="54"/>
+      <c r="E755" s="54"/>
+      <c r="F755" s="54"/>
+      <c r="G755" s="54"/>
+      <c r="H755" s="54"/>
+      <c r="I755" s="54"/>
+      <c r="J755" s="54"/>
+    </row>
+    <row r="756" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A756" s="54"/>
+      <c r="B756" s="54"/>
+      <c r="C756" s="54"/>
+      <c r="D756" s="54"/>
+      <c r="E756" s="54"/>
+      <c r="F756" s="54"/>
+      <c r="G756" s="54"/>
+      <c r="H756" s="54"/>
+      <c r="I756" s="54"/>
+      <c r="J756" s="54"/>
+    </row>
+    <row r="757" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A757" s="54" t="s">
         <v>1875</v>
       </c>
-      <c r="B757" s="51"/>
-      <c r="C757" s="51"/>
-      <c r="D757" s="51"/>
-      <c r="E757" s="51"/>
-      <c r="F757" s="51"/>
-      <c r="G757" s="51"/>
-      <c r="H757" s="51"/>
-    </row>
-    <row r="758" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A758" s="51"/>
-      <c r="B758" s="51"/>
-      <c r="C758" s="51"/>
-      <c r="D758" s="51"/>
-      <c r="E758" s="51"/>
-      <c r="F758" s="51"/>
-      <c r="G758" s="51"/>
-      <c r="H758" s="51"/>
-    </row>
-    <row r="759" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A759" s="51"/>
-      <c r="B759" s="51"/>
-      <c r="C759" s="51"/>
-      <c r="D759" s="51"/>
-      <c r="E759" s="51"/>
-      <c r="F759" s="51"/>
-      <c r="G759" s="51"/>
-      <c r="H759" s="51"/>
-    </row>
-    <row r="760" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A760" s="51" t="s">
+      <c r="B757" s="54"/>
+      <c r="C757" s="54"/>
+      <c r="D757" s="54"/>
+      <c r="E757" s="54"/>
+      <c r="F757" s="54"/>
+      <c r="G757" s="54"/>
+      <c r="H757" s="54"/>
+    </row>
+    <row r="758" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A758" s="54"/>
+      <c r="B758" s="54"/>
+      <c r="C758" s="54"/>
+      <c r="D758" s="54"/>
+      <c r="E758" s="54"/>
+      <c r="F758" s="54"/>
+      <c r="G758" s="54"/>
+      <c r="H758" s="54"/>
+    </row>
+    <row r="759" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A759" s="54"/>
+      <c r="B759" s="54"/>
+      <c r="C759" s="54"/>
+      <c r="D759" s="54"/>
+      <c r="E759" s="54"/>
+      <c r="F759" s="54"/>
+      <c r="G759" s="54"/>
+      <c r="H759" s="54"/>
+    </row>
+    <row r="760" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A760" s="54" t="s">
         <v>1876</v>
       </c>
-      <c r="B760" s="51"/>
-      <c r="C760" s="51"/>
-      <c r="D760" s="51"/>
-      <c r="E760" s="51"/>
-      <c r="F760" s="51"/>
-      <c r="G760" s="51"/>
-      <c r="H760" s="51"/>
-    </row>
-    <row r="761" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A761" s="51"/>
-      <c r="B761" s="51"/>
-      <c r="C761" s="51"/>
-      <c r="D761" s="51"/>
-      <c r="E761" s="51"/>
-      <c r="F761" s="51"/>
-      <c r="G761" s="51"/>
-      <c r="H761" s="51"/>
-    </row>
-    <row r="762" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A762" s="51"/>
-      <c r="B762" s="51"/>
-      <c r="C762" s="51"/>
-      <c r="D762" s="51"/>
-      <c r="E762" s="51"/>
-      <c r="F762" s="51"/>
-      <c r="G762" s="51"/>
-      <c r="H762" s="51"/>
+      <c r="B760" s="54"/>
+      <c r="C760" s="54"/>
+      <c r="D760" s="54"/>
+      <c r="E760" s="54"/>
+      <c r="F760" s="54"/>
+      <c r="G760" s="54"/>
+      <c r="H760" s="54"/>
+    </row>
+    <row r="761" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A761" s="54"/>
+      <c r="B761" s="54"/>
+      <c r="C761" s="54"/>
+      <c r="D761" s="54"/>
+      <c r="E761" s="54"/>
+      <c r="F761" s="54"/>
+      <c r="G761" s="54"/>
+      <c r="H761" s="54"/>
+    </row>
+    <row r="762" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A762" s="54"/>
+      <c r="B762" s="54"/>
+      <c r="C762" s="54"/>
+      <c r="D762" s="54"/>
+      <c r="E762" s="54"/>
+      <c r="F762" s="54"/>
+      <c r="G762" s="54"/>
+      <c r="H762" s="54"/>
     </row>
   </sheetData>
   <mergeCells count="4">
